--- a/filesystem/MarketingOps/CRM/Q4_2025_crm_export.xlsx
+++ b/filesystem/MarketingOps/CRM/Q4_2025_crm_export.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Footer" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Footer" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$J$211</definedName>
@@ -163,7 +163,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -271,11 +271,123 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000EA5E9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000EA5E9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -450,6 +562,12 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -773,9 +891,6 @@
           <t>Q4 2025 CRM Lead &amp; Opportunity Export</t>
         </is>
       </c>
-      <c r="B1" s="30" t="n"/>
-      <c r="C1" s="30" t="n"/>
-      <c r="D1" s="30" t="n"/>
     </row>
     <row r="2" ht="14" customHeight="1"/>
     <row r="3" ht="23" customHeight="1">
@@ -789,8 +904,8 @@
           <t>/MarketingOps/CRM/Q4_2025_crm_export.xlsx</t>
         </is>
       </c>
-      <c r="C3" s="32" t="n"/>
-      <c r="D3" s="32" t="n"/>
+      <c r="C3" s="62" t="n"/>
+      <c r="D3" s="63" t="n"/>
     </row>
     <row r="4" ht="23" customHeight="1">
       <c r="A4" s="31" t="inlineStr">
@@ -803,8 +918,8 @@
           <t>Grace Feldman, Director, Analytics &amp; Reporting</t>
         </is>
       </c>
-      <c r="C4" s="32" t="n"/>
-      <c r="D4" s="32" t="n"/>
+      <c r="C4" s="62" t="n"/>
+      <c r="D4" s="63" t="n"/>
     </row>
     <row r="5" ht="23" customHeight="1">
       <c r="A5" s="31" t="inlineStr">
@@ -817,8 +932,8 @@
           <t>ERPNext CRM (erp.thornfieldlsm.com) — Lead &amp; Opportunity module (Frappe/ERPNext v14)</t>
         </is>
       </c>
-      <c r="C5" s="32" t="n"/>
-      <c r="D5" s="32" t="n"/>
+      <c r="C5" s="62" t="n"/>
+      <c r="D5" s="63" t="n"/>
     </row>
     <row r="6" ht="23" customHeight="1">
       <c r="A6" s="31" t="inlineStr">
@@ -831,8 +946,8 @@
           <t>10/01/2025 – 12/31/2025 (Q4 2025)</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="32" t="n"/>
+      <c r="C6" s="62" t="n"/>
+      <c r="D6" s="63" t="n"/>
     </row>
     <row r="7" ht="23" customHeight="1">
       <c r="A7" s="31" t="inlineStr">
@@ -845,8 +960,8 @@
           <t>01/06/2026 09:47 EST</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n"/>
-      <c r="D7" s="32" t="n"/>
+      <c r="C7" s="62" t="n"/>
+      <c r="D7" s="63" t="n"/>
     </row>
     <row r="8" ht="23" customHeight="1">
       <c r="A8" s="31" t="inlineStr">
@@ -859,8 +974,8 @@
           <t>Analytics &amp; Reporting</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="32" t="n"/>
+      <c r="C8" s="62" t="n"/>
+      <c r="D8" s="63" t="n"/>
     </row>
     <row r="9" ht="10" customHeight="1"/>
     <row r="10" ht="10" customHeight="1"/>
@@ -870,9 +985,6 @@
           <t>Extract Summary</t>
         </is>
       </c>
-      <c r="B11" s="33" t="n"/>
-      <c r="C11" s="33" t="n"/>
-      <c r="D11" s="33" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="34" t="inlineStr">
@@ -885,8 +997,8 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="n"/>
+      <c r="C12" s="64" t="n"/>
+      <c r="D12" s="65" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="36" t="inlineStr">
@@ -897,8 +1009,8 @@
       <c r="B13" s="37" t="n">
         <v>210</v>
       </c>
-      <c r="C13" s="38" t="n"/>
-      <c r="D13" s="38" t="n"/>
+      <c r="C13" s="66" t="n"/>
+      <c r="D13" s="67" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="39" t="inlineStr">
@@ -909,8 +1021,8 @@
       <c r="B14" s="40" t="n">
         <v>142</v>
       </c>
-      <c r="C14" s="41" t="n"/>
-      <c r="D14" s="41" t="n"/>
+      <c r="C14" s="66" t="n"/>
+      <c r="D14" s="67" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="36" t="inlineStr">
@@ -921,8 +1033,8 @@
       <c r="B15" s="37" t="n">
         <v>68</v>
       </c>
-      <c r="C15" s="38" t="n"/>
-      <c r="D15" s="38" t="n"/>
+      <c r="C15" s="66" t="n"/>
+      <c r="D15" s="67" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="42" t="inlineStr">
@@ -935,8 +1047,8 @@
           <t>None (raw extract)</t>
         </is>
       </c>
-      <c r="C16" s="41" t="n"/>
-      <c r="D16" s="41" t="n"/>
+      <c r="C16" s="66" t="n"/>
+      <c r="D16" s="67" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="43" t="inlineStr">
@@ -949,8 +1061,8 @@
           <t>USD, format $#,##0</t>
         </is>
       </c>
-      <c r="C17" s="38" t="n"/>
-      <c r="D17" s="38" t="n"/>
+      <c r="C17" s="66" t="n"/>
+      <c r="D17" s="67" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="42" t="inlineStr">
@@ -963,8 +1075,8 @@
           <t>MM/DD/YYYY</t>
         </is>
       </c>
-      <c r="C18" s="41" t="n"/>
-      <c r="D18" s="41" t="n"/>
+      <c r="C18" s="66" t="n"/>
+      <c r="D18" s="67" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="43" t="inlineStr">
@@ -977,8 +1089,8 @@
           <t>Created Date ascending, then Lead ID</t>
         </is>
       </c>
-      <c r="C19" s="38" t="n"/>
-      <c r="D19" s="38" t="n"/>
+      <c r="C19" s="66" t="n"/>
+      <c r="D19" s="67" t="n"/>
     </row>
     <row r="20" ht="14" customHeight="1"/>
     <row r="21" ht="68" customHeight="1">
@@ -987,9 +1099,9 @@
           <t>Total rows: 210. This is the unfiltered CRM extract for Q4 2025 as pulled from the ERPNext Lead &amp; Opportunity module. Both Sales-Touched and Self-Serve Trial Lead Type values are present in the file; no downstream reporting filter has been applied at the export layer. Downstream rules governing which rows qualify for SQL-based pipeline calculations are documented separately in Analytics &amp; Reporting SOPs and are not re-stated here.</t>
         </is>
       </c>
-      <c r="B21" s="44" t="n"/>
-      <c r="C21" s="44" t="n"/>
-      <c r="D21" s="44" t="n"/>
+      <c r="B21" s="62" t="n"/>
+      <c r="C21" s="62" t="n"/>
+      <c r="D21" s="63" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -1022,7 +1134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J212"/>
+  <dimension ref="A1:J211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1102,12 +1214,12 @@
       </c>
       <c r="C2" s="41" t="inlineStr">
         <is>
-          <t>Amelia Rowe</t>
+          <t>Pia Nazarov</t>
         </is>
       </c>
       <c r="D2" s="49" t="inlineStr">
         <is>
-          <t>arowe@fenlanddx.com</t>
+          <t>p.nazarov@fenlanddx.com</t>
         </is>
       </c>
       <c r="E2" s="41" t="inlineStr">
@@ -1150,12 +1262,12 @@
       </c>
       <c r="C3" s="38" t="inlineStr">
         <is>
-          <t>Devon Blackthorne</t>
+          <t>Simone Petrov</t>
         </is>
       </c>
       <c r="D3" s="53" t="inlineStr">
         <is>
-          <t>d.blackthorne@corvexmol.com</t>
+          <t>s.petrov@corvexmol.com</t>
         </is>
       </c>
       <c r="E3" s="38" t="inlineStr">
@@ -1198,12 +1310,12 @@
       </c>
       <c r="C4" s="41" t="inlineStr">
         <is>
-          <t>Priyanka Iyer</t>
+          <t>Stellan Vasquez</t>
         </is>
       </c>
       <c r="D4" s="49" t="inlineStr">
         <is>
-          <t>piyer@radialbio.com</t>
+          <t>s.vasquez@radialbio.com</t>
         </is>
       </c>
       <c r="E4" s="41" t="inlineStr">
@@ -1246,12 +1358,12 @@
       </c>
       <c r="C5" s="38" t="inlineStr">
         <is>
-          <t>Nathan Osei</t>
+          <t>Felix Castellanos</t>
         </is>
       </c>
       <c r="D5" s="53" t="inlineStr">
         <is>
-          <t>nosei@larkspurbio.com</t>
+          <t>f.castellanos@larkspurbio.com</t>
         </is>
       </c>
       <c r="E5" s="38" t="inlineStr">
@@ -1294,12 +1406,12 @@
       </c>
       <c r="C6" s="41" t="inlineStr">
         <is>
-          <t>Kenji Nakamura</t>
+          <t>Ivaan Isaev</t>
         </is>
       </c>
       <c r="D6" s="49" t="inlineStr">
         <is>
-          <t>k.nakamura@ashcroftassays.com</t>
+          <t>i.isaev@ashcroftassays.com</t>
         </is>
       </c>
       <c r="E6" s="41" t="inlineStr">
@@ -1342,12 +1454,12 @@
       </c>
       <c r="C7" s="38" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Sanjay Manaia</t>
         </is>
       </c>
       <c r="D7" s="53" t="inlineStr">
         <is>
-          <t>s.marchetti@bellwetherreagents.com</t>
+          <t>s.manaia@bellwetherreagents.com</t>
         </is>
       </c>
       <c r="E7" s="38" t="inlineStr">
@@ -1390,12 +1502,12 @@
       </c>
       <c r="C8" s="41" t="inlineStr">
         <is>
-          <t>Marcus Weiss</t>
+          <t>Talia Kallas</t>
         </is>
       </c>
       <c r="D8" s="49" t="inlineStr">
         <is>
-          <t>mweiss@halcyonanalytical.com</t>
+          <t>t.kallas@halcyonanalytical.com</t>
         </is>
       </c>
       <c r="E8" s="41" t="inlineStr">
@@ -1438,12 +1550,12 @@
       </c>
       <c r="C9" s="38" t="inlineStr">
         <is>
-          <t>Anaya Patel</t>
+          <t>Aroha Radu</t>
         </is>
       </c>
       <c r="D9" s="53" t="inlineStr">
         <is>
-          <t>apatel@meadowbrookgx.com</t>
+          <t>a.radu@meadowbrookgx.com</t>
         </is>
       </c>
       <c r="E9" s="38" t="inlineStr">
@@ -1486,12 +1598,12 @@
       </c>
       <c r="C10" s="41" t="inlineStr">
         <is>
-          <t>Richard Ainsley</t>
+          <t>Nathan Mancini</t>
         </is>
       </c>
       <c r="D10" s="49" t="inlineStr">
         <is>
-          <t>r.ainsley2@silverpinetx.com</t>
+          <t>n.mancini@silverpinetx.com</t>
         </is>
       </c>
       <c r="E10" s="41" t="inlineStr">
@@ -1534,12 +1646,12 @@
       </c>
       <c r="C11" s="38" t="inlineStr">
         <is>
-          <t>Elena Baumann</t>
+          <t>Ravi Janik</t>
         </is>
       </c>
       <c r="D11" s="53" t="inlineStr">
         <is>
-          <t>ebaumann@windrowsci.com</t>
+          <t>r.janik@windrowsci.com</t>
         </is>
       </c>
       <c r="E11" s="38" t="inlineStr">
@@ -1582,12 +1694,12 @@
       </c>
       <c r="C12" s="41" t="inlineStr">
         <is>
-          <t>Ingrid Larsen</t>
+          <t>Paloma Okafor</t>
         </is>
       </c>
       <c r="D12" s="49" t="inlineStr">
         <is>
-          <t>ilarsen@norwichbio.com</t>
+          <t>p.okafor@norwichbio.com</t>
         </is>
       </c>
       <c r="E12" s="41" t="inlineStr">
@@ -1630,12 +1742,12 @@
       </c>
       <c r="C13" s="38" t="inlineStr">
         <is>
-          <t>Hassan Al-Rashid</t>
+          <t>Gustav Dahl</t>
         </is>
       </c>
       <c r="D13" s="53" t="inlineStr">
         <is>
-          <t>halrashid@kestreldx.com</t>
+          <t>g.dahl@kestreldx.com</t>
         </is>
       </c>
       <c r="E13" s="38" t="inlineStr">
@@ -1678,12 +1790,12 @@
       </c>
       <c r="C14" s="41" t="inlineStr">
         <is>
-          <t>Rachel Cortez</t>
+          <t>Pia Beringer</t>
         </is>
       </c>
       <c r="D14" s="49" t="inlineStr">
         <is>
-          <t>rcortez@northgatebiolabs.com</t>
+          <t>p.beringer@northgatebiolabs.com</t>
         </is>
       </c>
       <c r="E14" s="41" t="inlineStr">
@@ -1726,12 +1838,12 @@
       </c>
       <c r="C15" s="38" t="inlineStr">
         <is>
-          <t>Jamal Booker</t>
+          <t>Priyanka Zimmerman</t>
         </is>
       </c>
       <c r="D15" s="53" t="inlineStr">
         <is>
-          <t>jbooker@sedgwickreagents.com</t>
+          <t>p.zimmerman@sedgwickreagents.com</t>
         </is>
       </c>
       <c r="E15" s="38" t="inlineStr">
@@ -1774,12 +1886,12 @@
       </c>
       <c r="C16" s="41" t="inlineStr">
         <is>
-          <t>Petra Volkov</t>
+          <t>Malia Orozco</t>
         </is>
       </c>
       <c r="D16" s="49" t="inlineStr">
         <is>
-          <t>pvolkov@ashvalemol.com</t>
+          <t>m.orozco@ashvalemol.com</t>
         </is>
       </c>
       <c r="E16" s="41" t="inlineStr">
@@ -1822,12 +1934,12 @@
       </c>
       <c r="C17" s="38" t="inlineStr">
         <is>
-          <t>Deepak Ramaswamy</t>
+          <t>Kenji Moreau</t>
         </is>
       </c>
       <c r="D17" s="53" t="inlineStr">
         <is>
-          <t>dramaswamy@chartwellinst.com</t>
+          <t>k.moreau@chartwellinst.com</t>
         </is>
       </c>
       <c r="E17" s="38" t="inlineStr">
@@ -1870,12 +1982,12 @@
       </c>
       <c r="C18" s="41" t="inlineStr">
         <is>
-          <t>Aisha Khan</t>
+          <t>Tariq Onyekachi</t>
         </is>
       </c>
       <c r="D18" s="49" t="inlineStr">
         <is>
-          <t>akhan@draycottgx.com</t>
+          <t>t.onyekachi@draycottgx.com</t>
         </is>
       </c>
       <c r="E18" s="41" t="inlineStr">
@@ -1918,12 +2030,12 @@
       </c>
       <c r="C19" s="38" t="inlineStr">
         <is>
-          <t>Klaus Baumann</t>
+          <t>Deepak Beaulieu</t>
         </is>
       </c>
       <c r="D19" s="53" t="inlineStr">
         <is>
-          <t>kbaumann@elmwoodbio.com</t>
+          <t>d.beaulieu@elmwoodbio.com</t>
         </is>
       </c>
       <c r="E19" s="38" t="inlineStr">
@@ -1966,12 +2078,12 @@
       </c>
       <c r="C20" s="41" t="inlineStr">
         <is>
-          <t>Priya Menon</t>
+          <t>Stellan Ulrich</t>
         </is>
       </c>
       <c r="D20" s="49" t="inlineStr">
         <is>
-          <t>pmenon@ferncliffdx.com</t>
+          <t>s.ulrich@ferncliffdx.com</t>
         </is>
       </c>
       <c r="E20" s="41" t="inlineStr">
@@ -2014,12 +2126,12 @@
       </c>
       <c r="C21" s="38" t="inlineStr">
         <is>
-          <t>Yuki Sato</t>
+          <t>Petra Cabrera</t>
         </is>
       </c>
       <c r="D21" s="53" t="inlineStr">
         <is>
-          <t>ysato@gairlochanalytical.com</t>
+          <t>p.cabrera@gairlochanalytical.com</t>
         </is>
       </c>
       <c r="E21" s="38" t="inlineStr">
@@ -2062,12 +2174,12 @@
       </c>
       <c r="C22" s="41" t="inlineStr">
         <is>
-          <t>Fatima Farouk</t>
+          <t>Boris Baumann</t>
         </is>
       </c>
       <c r="D22" s="49" t="inlineStr">
         <is>
-          <t>ffarouk@harborlightbio.com</t>
+          <t>b.baumann@harborlightbio.com</t>
         </is>
       </c>
       <c r="E22" s="41" t="inlineStr">
@@ -2110,12 +2222,12 @@
       </c>
       <c r="C23" s="38" t="inlineStr">
         <is>
-          <t>Owen Booker</t>
+          <t>Umar Delgado</t>
         </is>
       </c>
       <c r="D23" s="53" t="inlineStr">
         <is>
-          <t>obooker@isleyreagents.com</t>
+          <t>u.delgado@isleyreagents.com</t>
         </is>
       </c>
       <c r="E23" s="38" t="inlineStr">
@@ -2158,12 +2270,12 @@
       </c>
       <c r="C24" s="41" t="inlineStr">
         <is>
-          <t>Rangi Osei</t>
+          <t>Kofi Farouk</t>
         </is>
       </c>
       <c r="D24" s="49" t="inlineStr">
         <is>
-          <t>rosei@jerbrookdx.com</t>
+          <t>k.farouk@jerbrookdx.com</t>
         </is>
       </c>
       <c r="E24" s="41" t="inlineStr">
@@ -2206,12 +2318,12 @@
       </c>
       <c r="C25" s="38" t="inlineStr">
         <is>
-          <t>Ana Silva</t>
+          <t>Owen Nazarov</t>
         </is>
       </c>
       <c r="D25" s="53" t="inlineStr">
         <is>
-          <t>asilva@kilburnmol.com</t>
+          <t>o.nazarov@kilburnmol.com</t>
         </is>
       </c>
       <c r="E25" s="38" t="inlineStr">
@@ -2254,12 +2366,12 @@
       </c>
       <c r="C26" s="41" t="inlineStr">
         <is>
-          <t>Vikram Nair</t>
+          <t>Devon Mancini</t>
         </is>
       </c>
       <c r="D26" s="49" t="inlineStr">
         <is>
-          <t>vnair@ledburyassays.com</t>
+          <t>d.mancini@ledburyassays.com</t>
         </is>
       </c>
       <c r="E26" s="41" t="inlineStr">
@@ -2302,12 +2414,12 @@
       </c>
       <c r="C27" s="38" t="inlineStr">
         <is>
-          <t>Sanjay Krishnamurthy</t>
+          <t>Devon Eriksson</t>
         </is>
       </c>
       <c r="D27" s="53" t="inlineStr">
         <is>
-          <t>s.krishnamurthy@meritbio.com</t>
+          <t>d.eriksson@meritbio.com</t>
         </is>
       </c>
       <c r="E27" s="38" t="inlineStr">
@@ -2350,12 +2462,12 @@
       </c>
       <c r="C28" s="41" t="inlineStr">
         <is>
-          <t>Elena Cortez</t>
+          <t>Wei Al-Sayed</t>
         </is>
       </c>
       <c r="D28" s="49" t="inlineStr">
         <is>
-          <t>ecortez@newburyinst.com</t>
+          <t>w.al-sayed@newburyinst.com</t>
         </is>
       </c>
       <c r="E28" s="41" t="inlineStr">
@@ -2398,12 +2510,12 @@
       </c>
       <c r="C29" s="38" t="inlineStr">
         <is>
-          <t>Chen Wei</t>
+          <t>Kenji Sokolova</t>
         </is>
       </c>
       <c r="D29" s="53" t="inlineStr">
         <is>
-          <t>cwei@orleansgx.com</t>
+          <t>k.sokolova@orleansgx.com</t>
         </is>
       </c>
       <c r="E29" s="38" t="inlineStr">
@@ -2446,12 +2558,12 @@
       </c>
       <c r="C30" s="41" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Sofia Vasquez</t>
         </is>
       </c>
       <c r="D30" s="49" t="inlineStr">
         <is>
-          <t>rsharma@pembertondx.com</t>
+          <t>s.vasquez@pembertondx.com</t>
         </is>
       </c>
       <c r="E30" s="41" t="inlineStr">
@@ -2494,12 +2606,12 @@
       </c>
       <c r="C31" s="38" t="inlineStr">
         <is>
-          <t>Naveen Chandra</t>
+          <t>Malia Rivas</t>
         </is>
       </c>
       <c r="D31" s="53" t="inlineStr">
         <is>
-          <t>nchandra@quentonbiolabs.com</t>
+          <t>m.rivas@quentonbiolabs.com</t>
         </is>
       </c>
       <c r="E31" s="38" t="inlineStr">
@@ -2542,12 +2654,12 @@
       </c>
       <c r="C32" s="41" t="inlineStr">
         <is>
-          <t>Malia Kekoa</t>
+          <t>Edvard Ferreira</t>
         </is>
       </c>
       <c r="D32" s="49" t="inlineStr">
         <is>
-          <t>mkekoa@ramseyanalytical.com</t>
+          <t>e.ferreira@ramseyanalytical.com</t>
         </is>
       </c>
       <c r="E32" s="41" t="inlineStr">
@@ -2590,12 +2702,12 @@
       </c>
       <c r="C33" s="38" t="inlineStr">
         <is>
-          <t>Boris Sokolov</t>
+          <t>Wren Kekoa</t>
         </is>
       </c>
       <c r="D33" s="53" t="inlineStr">
         <is>
-          <t>bsokolov@sutherlandreagents.com</t>
+          <t>w.kekoa@sutherlandreagents.com</t>
         </is>
       </c>
       <c r="E33" s="38" t="inlineStr">
@@ -2638,12 +2750,12 @@
       </c>
       <c r="C34" s="41" t="inlineStr">
         <is>
-          <t>Zara Ahmed</t>
+          <t>Esther Kapoor</t>
         </is>
       </c>
       <c r="D34" s="49" t="inlineStr">
         <is>
-          <t>zahmed@trellismol.com</t>
+          <t>e.kapoor@trellismol.com</t>
         </is>
       </c>
       <c r="E34" s="41" t="inlineStr">
@@ -2686,12 +2798,12 @@
       </c>
       <c r="C35" s="38" t="inlineStr">
         <is>
-          <t>Amir Hassan</t>
+          <t>Nia Papadopoulos</t>
         </is>
       </c>
       <c r="D35" s="53" t="inlineStr">
         <is>
-          <t>ahassan@underhillbio.com</t>
+          <t>n.papadopoulos@underhillbio.com</t>
         </is>
       </c>
       <c r="E35" s="38" t="inlineStr">
@@ -2734,12 +2846,12 @@
       </c>
       <c r="C36" s="41" t="inlineStr">
         <is>
-          <t>Ananya Iyer</t>
+          <t>Aisha Novak</t>
         </is>
       </c>
       <c r="D36" s="49" t="inlineStr">
         <is>
-          <t>aiyer@veronaassays.com</t>
+          <t>a.novak@veronaassays.com</t>
         </is>
       </c>
       <c r="E36" s="41" t="inlineStr">
@@ -2782,12 +2894,12 @@
       </c>
       <c r="C37" s="38" t="inlineStr">
         <is>
-          <t>Richard Ainsley</t>
+          <t>Kenji Rivas</t>
         </is>
       </c>
       <c r="D37" s="53" t="inlineStr">
         <is>
-          <t>richard.ainsley@whitfielddx.com</t>
+          <t>k.rivas@whitfielddx.com</t>
         </is>
       </c>
       <c r="E37" s="38" t="inlineStr">
@@ -2830,12 +2942,12 @@
       </c>
       <c r="C38" s="41" t="inlineStr">
         <is>
-          <t>Farah Al-Sayed</t>
+          <t>Larisa Novak</t>
         </is>
       </c>
       <c r="D38" s="49" t="inlineStr">
         <is>
-          <t>falsayed@xantheinst.com</t>
+          <t>l.novak@xantheinst.com</t>
         </is>
       </c>
       <c r="E38" s="41" t="inlineStr">
@@ -2878,12 +2990,12 @@
       </c>
       <c r="C39" s="38" t="inlineStr">
         <is>
-          <t>Nikolai Petrov</t>
+          <t>Aroha Wei</t>
         </is>
       </c>
       <c r="D39" s="53" t="inlineStr">
         <is>
-          <t>npetrov@yorktownbio.com</t>
+          <t>a.wei@yorktownbio.com</t>
         </is>
       </c>
       <c r="E39" s="38" t="inlineStr">
@@ -2926,12 +3038,12 @@
       </c>
       <c r="C40" s="41" t="inlineStr">
         <is>
-          <t>Aroha Manaia</t>
+          <t>Idris Petrescu</t>
         </is>
       </c>
       <c r="D40" s="49" t="inlineStr">
         <is>
-          <t>amanaia@zephyrgx.com</t>
+          <t>i.petrescu@zephyrgx.com</t>
         </is>
       </c>
       <c r="E40" s="41" t="inlineStr">
@@ -2974,12 +3086,12 @@
       </c>
       <c r="C41" s="38" t="inlineStr">
         <is>
-          <t>Kai Nakamura</t>
+          <t>Giulia Quintero</t>
         </is>
       </c>
       <c r="D41" s="53" t="inlineStr">
         <is>
-          <t>knakamura@aldermandx.com</t>
+          <t>g.quintero@aldermandx.com</t>
         </is>
       </c>
       <c r="E41" s="38" t="inlineStr">
@@ -3022,12 +3134,12 @@
       </c>
       <c r="C42" s="41" t="inlineStr">
         <is>
-          <t>Aditi Rao</t>
+          <t>Priya Sato</t>
         </is>
       </c>
       <c r="D42" s="49" t="inlineStr">
         <is>
-          <t>arao@bosworthbio.com</t>
+          <t>p.sato@bosworthbio.com</t>
         </is>
       </c>
       <c r="E42" s="41" t="inlineStr">
@@ -3070,12 +3182,12 @@
       </c>
       <c r="C43" s="38" t="inlineStr">
         <is>
-          <t>Lena Ivanov</t>
+          <t>Idris Hoffmann</t>
         </is>
       </c>
       <c r="D43" s="53" t="inlineStr">
         <is>
-          <t>livanov@colvinreagents.com</t>
+          <t>i.hoffmann@colvinreagents.com</t>
         </is>
       </c>
       <c r="E43" s="38" t="inlineStr">
@@ -3118,12 +3230,12 @@
       </c>
       <c r="C44" s="41" t="inlineStr">
         <is>
-          <t>Ishaan Verma</t>
+          <t>Mikhail Marchand</t>
         </is>
       </c>
       <c r="D44" s="49" t="inlineStr">
         <is>
-          <t>iverma@deerfieldmol.com</t>
+          <t>m.marchand@deerfieldmol.com</t>
         </is>
       </c>
       <c r="E44" s="41" t="inlineStr">
@@ -3166,12 +3278,12 @@
       </c>
       <c r="C45" s="38" t="inlineStr">
         <is>
-          <t>Marcus Weiss</t>
+          <t>Idris Dahl</t>
         </is>
       </c>
       <c r="D45" s="53" t="inlineStr">
         <is>
-          <t>mweiss@estwickinst.com</t>
+          <t>i.dahl@estwickinst.com</t>
         </is>
       </c>
       <c r="E45" s="38" t="inlineStr">
@@ -3214,12 +3326,12 @@
       </c>
       <c r="C46" s="41" t="inlineStr">
         <is>
-          <t>Neha Kapoor</t>
+          <t>Bianca Baumann</t>
         </is>
       </c>
       <c r="D46" s="49" t="inlineStr">
         <is>
-          <t>nkapoor@fairhavenanalytical.com</t>
+          <t>b.baumann@fairhavenanalytical.com</t>
         </is>
       </c>
       <c r="E46" s="41" t="inlineStr">
@@ -3262,12 +3374,12 @@
       </c>
       <c r="C47" s="38" t="inlineStr">
         <is>
-          <t>Henry Beauchamp</t>
+          <t>Paloma Falcon</t>
         </is>
       </c>
       <c r="D47" s="53" t="inlineStr">
         <is>
-          <t>h.beauchamp2@glenridgebiolabs.com</t>
+          <t>p.falcon@glenridgebiolabs.com</t>
         </is>
       </c>
       <c r="E47" s="38" t="inlineStr">
@@ -3310,12 +3422,12 @@
       </c>
       <c r="C48" s="41" t="inlineStr">
         <is>
-          <t>Aarav Bhatt</t>
+          <t>Edvard Petrov</t>
         </is>
       </c>
       <c r="D48" s="49" t="inlineStr">
         <is>
-          <t>abhatt@halewooddx.com</t>
+          <t>e.petrov@halewooddx.com</t>
         </is>
       </c>
       <c r="E48" s="41" t="inlineStr">
@@ -3358,12 +3470,12 @@
       </c>
       <c r="C49" s="38" t="inlineStr">
         <is>
-          <t>Anika Menon</t>
+          <t>Yara Hoffmann</t>
         </is>
       </c>
       <c r="D49" s="53" t="inlineStr">
         <is>
-          <t>amenon@ivywoodassays.com</t>
+          <t>y.hoffmann@ivywoodassays.com</t>
         </is>
       </c>
       <c r="E49" s="38" t="inlineStr">
@@ -3406,12 +3518,12 @@
       </c>
       <c r="C50" s="41" t="inlineStr">
         <is>
-          <t>Petra Volkov</t>
+          <t>Mikhail Nikolic</t>
         </is>
       </c>
       <c r="D50" s="49" t="inlineStr">
         <is>
-          <t>pvolkov@junctionreagents.com</t>
+          <t>m.nikolic@junctionreagents.com</t>
         </is>
       </c>
       <c r="E50" s="41" t="inlineStr">
@@ -3454,12 +3566,12 @@
       </c>
       <c r="C51" s="38" t="inlineStr">
         <is>
-          <t>Devon Cabrera</t>
+          <t>Owen Mancini</t>
         </is>
       </c>
       <c r="D51" s="53" t="inlineStr">
         <is>
-          <t>dcabrera@keswickgx.com</t>
+          <t>o.mancini@keswickgx.com</t>
         </is>
       </c>
       <c r="E51" s="38" t="inlineStr">
@@ -3502,12 +3614,12 @@
       </c>
       <c r="C52" s="41" t="inlineStr">
         <is>
-          <t>Sun-Hi Ohaeri</t>
+          <t>Torsten Yilmaz</t>
         </is>
       </c>
       <c r="D52" s="49" t="inlineStr">
         <is>
-          <t>sohaeri@lyndhurstinst.com</t>
+          <t>t.yilmaz@lyndhurstinst.com</t>
         </is>
       </c>
       <c r="E52" s="41" t="inlineStr">
@@ -3550,12 +3662,12 @@
       </c>
       <c r="C53" s="38" t="inlineStr">
         <is>
-          <t>Yuki Sato</t>
+          <t>Petra Ustinov</t>
         </is>
       </c>
       <c r="D53" s="53" t="inlineStr">
         <is>
-          <t>ysato@marstonbio.com</t>
+          <t>p.ustinov@marstonbio.com</t>
         </is>
       </c>
       <c r="E53" s="38" t="inlineStr">
@@ -3598,12 +3710,12 @@
       </c>
       <c r="C54" s="41" t="inlineStr">
         <is>
-          <t>Amelia Rowe</t>
+          <t>Mateus Ainsley</t>
         </is>
       </c>
       <c r="D54" s="49" t="inlineStr">
         <is>
-          <t>amelia.rowe@oakenwooddx.com</t>
+          <t>m.ainsley@oakenwooddx.com</t>
         </is>
       </c>
       <c r="E54" s="41" t="inlineStr">
@@ -3646,12 +3758,12 @@
       </c>
       <c r="C55" s="38" t="inlineStr">
         <is>
-          <t>Klaus Baumann</t>
+          <t>Hana Moreau</t>
         </is>
       </c>
       <c r="D55" s="53" t="inlineStr">
         <is>
-          <t>kbaumann@pentworthmol.com</t>
+          <t>h.moreau@pentworthmol.com</t>
         </is>
       </c>
       <c r="E55" s="38" t="inlineStr">
@@ -3694,12 +3806,12 @@
       </c>
       <c r="C56" s="41" t="inlineStr">
         <is>
-          <t>Ivaan Sharma</t>
+          <t>Ishaan Janik</t>
         </is>
       </c>
       <c r="D56" s="49" t="inlineStr">
         <is>
-          <t>isharma@quaywaterbiolabs.com</t>
+          <t>i.janik@quaywaterbiolabs.com</t>
         </is>
       </c>
       <c r="E56" s="41" t="inlineStr">
@@ -3742,12 +3854,12 @@
       </c>
       <c r="C57" s="38" t="inlineStr">
         <is>
-          <t>Jamal Booker</t>
+          <t>Quentin Onyekachi</t>
         </is>
       </c>
       <c r="D57" s="53" t="inlineStr">
         <is>
-          <t>jbooker@rowtonreagents.com</t>
+          <t>q.onyekachi@rowtonreagents.com</t>
         </is>
       </c>
       <c r="E57" s="38" t="inlineStr">
@@ -3790,12 +3902,12 @@
       </c>
       <c r="C58" s="41" t="inlineStr">
         <is>
-          <t>Priyanka Iyer</t>
+          <t>Ana Ulrich</t>
         </is>
       </c>
       <c r="D58" s="49" t="inlineStr">
         <is>
-          <t>piyer@tavistockassays.com</t>
+          <t>a.ulrich@tavistockassays.com</t>
         </is>
       </c>
       <c r="E58" s="41" t="inlineStr">
@@ -3838,12 +3950,12 @@
       </c>
       <c r="C59" s="38" t="inlineStr">
         <is>
-          <t>Boris Sokolov</t>
+          <t>Xander Baumann</t>
         </is>
       </c>
       <c r="D59" s="53" t="inlineStr">
         <is>
-          <t>bsokolov@uxbridgegx.com</t>
+          <t>x.baumann@uxbridgegx.com</t>
         </is>
       </c>
       <c r="E59" s="38" t="inlineStr">
@@ -3886,12 +3998,12 @@
       </c>
       <c r="C60" s="41" t="inlineStr">
         <is>
-          <t>Diya Chandra</t>
+          <t>Esther Ustinov</t>
         </is>
       </c>
       <c r="D60" s="49" t="inlineStr">
         <is>
-          <t>dchandra@valloninst.com</t>
+          <t>e.ustinov@valloninst.com</t>
         </is>
       </c>
       <c r="E60" s="41" t="inlineStr">
@@ -3934,12 +4046,12 @@
       </c>
       <c r="C61" s="38" t="inlineStr">
         <is>
-          <t>Farah Al-Sayed</t>
+          <t>Xander Nowak</t>
         </is>
       </c>
       <c r="D61" s="53" t="inlineStr">
         <is>
-          <t>falsayed@wintergreenbio.com</t>
+          <t>x.nowak@wintergreenbio.com</t>
         </is>
       </c>
       <c r="E61" s="38" t="inlineStr">
@@ -3982,12 +4094,12 @@
       </c>
       <c r="C62" s="41" t="inlineStr">
         <is>
-          <t>Aroha Manaia</t>
+          <t>Quentin Beauchamp</t>
         </is>
       </c>
       <c r="D62" s="49" t="inlineStr">
         <is>
-          <t>amanaia@yardsleyanalytical.com</t>
+          <t>q.beauchamp@yardsleyanalytical.com</t>
         </is>
       </c>
       <c r="E62" s="41" t="inlineStr">
@@ -4030,12 +4142,12 @@
       </c>
       <c r="C63" s="38" t="inlineStr">
         <is>
-          <t>Rangi Osei</t>
+          <t>Farah Wisniewski</t>
         </is>
       </c>
       <c r="D63" s="53" t="inlineStr">
         <is>
-          <t>rosei@zenithbio.com</t>
+          <t>f.wisniewski@zenithbio.com</t>
         </is>
       </c>
       <c r="E63" s="38" t="inlineStr">
@@ -4078,12 +4190,12 @@
       </c>
       <c r="C64" s="41" t="inlineStr">
         <is>
-          <t>Nathan Cho</t>
+          <t>Pia Marchetti</t>
         </is>
       </c>
       <c r="D64" s="49" t="inlineStr">
         <is>
-          <t>ncho@wrenfieldscientific.com</t>
+          <t>p.marchetti@wrenfieldscientific.com</t>
         </is>
       </c>
       <c r="E64" s="41" t="inlineStr">
@@ -4126,12 +4238,12 @@
       </c>
       <c r="C65" s="38" t="inlineStr">
         <is>
-          <t>Aisha Khan</t>
+          <t>Callum Ostrowski</t>
         </is>
       </c>
       <c r="D65" s="53" t="inlineStr">
         <is>
-          <t>akhan@everglade-dx.com</t>
+          <t>c.ostrowski@everglade-dx.com</t>
         </is>
       </c>
       <c r="E65" s="38" t="inlineStr">
@@ -4174,12 +4286,12 @@
       </c>
       <c r="C66" s="41" t="inlineStr">
         <is>
-          <t>Vikram Nair</t>
+          <t>Petra Nowak</t>
         </is>
       </c>
       <c r="D66" s="49" t="inlineStr">
         <is>
-          <t>vnair@longacrelabs.com</t>
+          <t>p.nowak@longacrelabs.com</t>
         </is>
       </c>
       <c r="E66" s="41" t="inlineStr">
@@ -4222,12 +4334,12 @@
       </c>
       <c r="C67" s="38" t="inlineStr">
         <is>
-          <t>Elena Cortez</t>
+          <t>Lucas Volkov</t>
         </is>
       </c>
       <c r="D67" s="53" t="inlineStr">
         <is>
-          <t>ecortez@highfieldinst.com</t>
+          <t>l.volkov@highfieldinst.com</t>
         </is>
       </c>
       <c r="E67" s="38" t="inlineStr">
@@ -4270,12 +4382,12 @@
       </c>
       <c r="C68" s="41" t="inlineStr">
         <is>
-          <t>Kenji Nakamura</t>
+          <t>Noor Delgado</t>
         </is>
       </c>
       <c r="D68" s="49" t="inlineStr">
         <is>
-          <t>knakamura@hallmarkmol.com</t>
+          <t>n.delgado@hallmarkmol.com</t>
         </is>
       </c>
       <c r="E68" s="41" t="inlineStr">
@@ -4318,12 +4430,12 @@
       </c>
       <c r="C69" s="38" t="inlineStr">
         <is>
-          <t>Malia Kekoa</t>
+          <t>Kofi Ibori</t>
         </is>
       </c>
       <c r="D69" s="53" t="inlineStr">
         <is>
-          <t>mkekoa@palladiumassays.com</t>
+          <t>k.ibori@palladiumassays.com</t>
         </is>
       </c>
       <c r="E69" s="38" t="inlineStr">
@@ -4366,12 +4478,12 @@
       </c>
       <c r="C70" s="41" t="inlineStr">
         <is>
-          <t>Zara Ahmed</t>
+          <t>Lucas Ulrich</t>
         </is>
       </c>
       <c r="D70" s="49" t="inlineStr">
         <is>
-          <t>zahmed@coastwisereagents.com</t>
+          <t>l.ulrich@coastwisereagents.com</t>
         </is>
       </c>
       <c r="E70" s="41" t="inlineStr">
@@ -4414,12 +4526,12 @@
       </c>
       <c r="C71" s="38" t="inlineStr">
         <is>
-          <t>Ishaan Verma</t>
+          <t>Umar Sato</t>
         </is>
       </c>
       <c r="D71" s="53" t="inlineStr">
         <is>
-          <t>iverma@nettlefordbio.com</t>
+          <t>u.sato@nettlefordbio.com</t>
         </is>
       </c>
       <c r="E71" s="38" t="inlineStr">
@@ -4462,12 +4574,12 @@
       </c>
       <c r="C72" s="41" t="inlineStr">
         <is>
-          <t>Amir Hassan</t>
+          <t>Priyanka Janik</t>
         </is>
       </c>
       <c r="D72" s="49" t="inlineStr">
         <is>
-          <t>ahassan@kadencedx.com</t>
+          <t>p.janik@kadencedx.com</t>
         </is>
       </c>
       <c r="E72" s="41" t="inlineStr">
@@ -4510,12 +4622,12 @@
       </c>
       <c r="C73" s="38" t="inlineStr">
         <is>
-          <t>Petra Volkov</t>
+          <t>Deepak Iyer</t>
         </is>
       </c>
       <c r="D73" s="53" t="inlineStr">
         <is>
-          <t>pvolkov@ashlandgx.com</t>
+          <t>d.iyer@ashlandgx.com</t>
         </is>
       </c>
       <c r="E73" s="38" t="inlineStr">
@@ -4558,12 +4670,12 @@
       </c>
       <c r="C74" s="41" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Farah Krishnamurthy</t>
         </is>
       </c>
       <c r="D74" s="49" t="inlineStr">
         <is>
-          <t>s.marchetti@brixtonreagents.com</t>
+          <t>f.krishnamurthy@brixtonreagents.com</t>
         </is>
       </c>
       <c r="E74" s="41" t="inlineStr">
@@ -4606,12 +4718,12 @@
       </c>
       <c r="C75" s="38" t="inlineStr">
         <is>
-          <t>Ana Silva</t>
+          <t>Yuki Vukovic</t>
         </is>
       </c>
       <c r="D75" s="53" t="inlineStr">
         <is>
-          <t>asilva@willowmeredx.com</t>
+          <t>y.vukovic@willowmeredx.com</t>
         </is>
       </c>
       <c r="E75" s="38" t="inlineStr">
@@ -4654,12 +4766,12 @@
       </c>
       <c r="C76" s="41" t="inlineStr">
         <is>
-          <t>Chen Wei</t>
+          <t>Vikram Rivas</t>
         </is>
       </c>
       <c r="D76" s="49" t="inlineStr">
         <is>
-          <t>cwei@selbyinst.com</t>
+          <t>v.rivas@selbyinst.com</t>
         </is>
       </c>
       <c r="E76" s="41" t="inlineStr">
@@ -4702,12 +4814,12 @@
       </c>
       <c r="C77" s="38" t="inlineStr">
         <is>
-          <t>Deepak Ramaswamy</t>
+          <t>Bianca Vukovic</t>
         </is>
       </c>
       <c r="D77" s="53" t="inlineStr">
         <is>
-          <t>dramaswamy@thornburybio.com</t>
+          <t>b.vukovic@thornburybio.com</t>
         </is>
       </c>
       <c r="E77" s="38" t="inlineStr">
@@ -4750,12 +4862,12 @@
       </c>
       <c r="C78" s="41" t="inlineStr">
         <is>
-          <t>Rachel Cortez</t>
+          <t>Selin Ahmed</t>
         </is>
       </c>
       <c r="D78" s="49" t="inlineStr">
         <is>
-          <t>rcortez@argentmol.com</t>
+          <t>s.ahmed@argentmol.com</t>
         </is>
       </c>
       <c r="E78" s="41" t="inlineStr">
@@ -4798,12 +4910,12 @@
       </c>
       <c r="C79" s="38" t="inlineStr">
         <is>
-          <t>Richard Ainsley</t>
+          <t>Keiko Rowe</t>
         </is>
       </c>
       <c r="D79" s="53" t="inlineStr">
         <is>
-          <t>r.ainsley2@beaconassay.com</t>
+          <t>k.rowe@beaconassay.com</t>
         </is>
       </c>
       <c r="E79" s="38" t="inlineStr">
@@ -4846,12 +4958,12 @@
       </c>
       <c r="C80" s="41" t="inlineStr">
         <is>
-          <t>Fatima Farouk</t>
+          <t>Jonas Enescu</t>
         </is>
       </c>
       <c r="D80" s="49" t="inlineStr">
         <is>
-          <t>ffarouk@coveinst.com</t>
+          <t>j.enescu@coveinst.com</t>
         </is>
       </c>
       <c r="E80" s="41" t="inlineStr">
@@ -4894,12 +5006,12 @@
       </c>
       <c r="C81" s="38" t="inlineStr">
         <is>
-          <t>Owen Booker</t>
+          <t>Simone Vasquez</t>
         </is>
       </c>
       <c r="D81" s="53" t="inlineStr">
         <is>
-          <t>obooker@delaneybio.com</t>
+          <t>s.vasquez@delaneybio.com</t>
         </is>
       </c>
       <c r="E81" s="38" t="inlineStr">
@@ -4942,12 +5054,12 @@
       </c>
       <c r="C82" s="41" t="inlineStr">
         <is>
-          <t>Aditi Rao</t>
+          <t>Nikolai Papadopoulos</t>
         </is>
       </c>
       <c r="D82" s="49" t="inlineStr">
         <is>
-          <t>arao@enfieldreagents.com</t>
+          <t>n.papadopoulos@enfieldreagents.com</t>
         </is>
       </c>
       <c r="E82" s="41" t="inlineStr">
@@ -4990,12 +5102,12 @@
       </c>
       <c r="C83" s="38" t="inlineStr">
         <is>
-          <t>Kenji Nakamura</t>
+          <t>Magnus Rivas</t>
         </is>
       </c>
       <c r="D83" s="53" t="inlineStr">
         <is>
-          <t>k.nakamura@fenlanddx.com</t>
+          <t>m.rivas@fenlanddx.com</t>
         </is>
       </c>
       <c r="E83" s="38" t="inlineStr">
@@ -5038,12 +5150,12 @@
       </c>
       <c r="C84" s="41" t="inlineStr">
         <is>
-          <t>Elena Baumann</t>
+          <t>Elena Isaev</t>
         </is>
       </c>
       <c r="D84" s="49" t="inlineStr">
         <is>
-          <t>ebaumann@corvexmol.com</t>
+          <t>e.isaev@corvexmol.com</t>
         </is>
       </c>
       <c r="E84" s="41" t="inlineStr">
@@ -5086,12 +5198,12 @@
       </c>
       <c r="C85" s="38" t="inlineStr">
         <is>
-          <t>Naveen Chandra</t>
+          <t>Priyanka Gagnon</t>
         </is>
       </c>
       <c r="D85" s="53" t="inlineStr">
         <is>
-          <t>nchandra@radialbio.com</t>
+          <t>p.gagnon@radialbio.com</t>
         </is>
       </c>
       <c r="E85" s="38" t="inlineStr">
@@ -5134,12 +5246,12 @@
       </c>
       <c r="C86" s="41" t="inlineStr">
         <is>
-          <t>Klaus Baumann</t>
+          <t>Henry Radu</t>
         </is>
       </c>
       <c r="D86" s="49" t="inlineStr">
         <is>
-          <t>kbaumann@larkspurbio.com</t>
+          <t>h.radu@larkspurbio.com</t>
         </is>
       </c>
       <c r="E86" s="41" t="inlineStr">
@@ -5182,12 +5294,12 @@
       </c>
       <c r="C87" s="38" t="inlineStr">
         <is>
-          <t>Priya Menon</t>
+          <t>Wei Onyekachi</t>
         </is>
       </c>
       <c r="D87" s="53" t="inlineStr">
         <is>
-          <t>pmenon@ashcroftassays.com</t>
+          <t>w.onyekachi@ashcroftassays.com</t>
         </is>
       </c>
       <c r="E87" s="38" t="inlineStr">
@@ -5230,12 +5342,12 @@
       </c>
       <c r="C88" s="41" t="inlineStr">
         <is>
-          <t>Amelia Rowe</t>
+          <t>Malia Chandra</t>
         </is>
       </c>
       <c r="D88" s="49" t="inlineStr">
         <is>
-          <t>arowe@bellwetherreagents.com</t>
+          <t>m.chandra@bellwetherreagents.com</t>
         </is>
       </c>
       <c r="E88" s="41" t="inlineStr">
@@ -5278,12 +5390,12 @@
       </c>
       <c r="C89" s="38" t="inlineStr">
         <is>
-          <t>Boris Sokolov</t>
+          <t>Dahlia Marchand</t>
         </is>
       </c>
       <c r="D89" s="53" t="inlineStr">
         <is>
-          <t>bsokolov@halcyonanalytical.com</t>
+          <t>d.marchand@halcyonanalytical.com</t>
         </is>
       </c>
       <c r="E89" s="38" t="inlineStr">
@@ -5326,12 +5438,12 @@
       </c>
       <c r="C90" s="41" t="inlineStr">
         <is>
-          <t>Aroha Manaia</t>
+          <t>Amir Wisniewski</t>
         </is>
       </c>
       <c r="D90" s="49" t="inlineStr">
         <is>
-          <t>amanaia@meadowbrookgx.com</t>
+          <t>a.wisniewski@meadowbrookgx.com</t>
         </is>
       </c>
       <c r="E90" s="41" t="inlineStr">
@@ -5374,12 +5486,12 @@
       </c>
       <c r="C91" s="38" t="inlineStr">
         <is>
-          <t>Nikolai Petrov</t>
+          <t>Zane Ibori</t>
         </is>
       </c>
       <c r="D91" s="53" t="inlineStr">
         <is>
-          <t>npetrov@silverpinetx.com</t>
+          <t>z.ibori@silverpinetx.com</t>
         </is>
       </c>
       <c r="E91" s="38" t="inlineStr">
@@ -5422,12 +5534,12 @@
       </c>
       <c r="C92" s="41" t="inlineStr">
         <is>
-          <t>Ananya Iyer</t>
+          <t>Leila Cabrera</t>
         </is>
       </c>
       <c r="D92" s="49" t="inlineStr">
         <is>
-          <t>aiyer@windrowsci.com</t>
+          <t>l.cabrera@windrowsci.com</t>
         </is>
       </c>
       <c r="E92" s="41" t="inlineStr">
@@ -5470,12 +5582,12 @@
       </c>
       <c r="C93" s="38" t="inlineStr">
         <is>
-          <t>Devon Cabrera</t>
+          <t>Cormac Osei</t>
         </is>
       </c>
       <c r="D93" s="53" t="inlineStr">
         <is>
-          <t>dcabrera@norwichbio.com</t>
+          <t>c.osei@norwichbio.com</t>
         </is>
       </c>
       <c r="E93" s="38" t="inlineStr">
@@ -5518,12 +5630,12 @@
       </c>
       <c r="C94" s="41" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Cormac Nazarov</t>
         </is>
       </c>
       <c r="D94" s="49" t="inlineStr">
         <is>
-          <t>rsharma@kestreldx.com</t>
+          <t>c.nazarov@kestreldx.com</t>
         </is>
       </c>
       <c r="E94" s="41" t="inlineStr">
@@ -5566,12 +5678,12 @@
       </c>
       <c r="C95" s="38" t="inlineStr">
         <is>
-          <t>Sanjay Krishnamurthy</t>
+          <t>Quinn Ainsley</t>
         </is>
       </c>
       <c r="D95" s="53" t="inlineStr">
         <is>
-          <t>s.krishnamurthy@northgatebiolabs.com</t>
+          <t>q.ainsley@northgatebiolabs.com</t>
         </is>
       </c>
       <c r="E95" s="38" t="inlineStr">
@@ -5614,12 +5726,12 @@
       </c>
       <c r="C96" s="41" t="inlineStr">
         <is>
-          <t>Anika Menon</t>
+          <t>Vikram Nakamura</t>
         </is>
       </c>
       <c r="D96" s="49" t="inlineStr">
         <is>
-          <t>amenon@sedgwickreagents.com</t>
+          <t>v.nakamura@sedgwickreagents.com</t>
         </is>
       </c>
       <c r="E96" s="41" t="inlineStr">
@@ -5662,12 +5774,12 @@
       </c>
       <c r="C97" s="38" t="inlineStr">
         <is>
-          <t>Henry Beauchamp</t>
+          <t>Klaus Enescu</t>
         </is>
       </c>
       <c r="D97" s="53" t="inlineStr">
         <is>
-          <t>h.beauchamp2@ashvalemol.com</t>
+          <t>k.enescu@ashvalemol.com</t>
         </is>
       </c>
       <c r="E97" s="38" t="inlineStr">
@@ -5710,12 +5822,12 @@
       </c>
       <c r="C98" s="41" t="inlineStr">
         <is>
-          <t>Zara Ahmed</t>
+          <t>Vikram Volkov</t>
         </is>
       </c>
       <c r="D98" s="49" t="inlineStr">
         <is>
-          <t>zahmed@chartwellinst.com</t>
+          <t>v.volkov@chartwellinst.com</t>
         </is>
       </c>
       <c r="E98" s="41" t="inlineStr">
@@ -5758,12 +5870,12 @@
       </c>
       <c r="C99" s="38" t="inlineStr">
         <is>
-          <t>Lena Ivanov</t>
+          <t>Larisa Ulrich</t>
         </is>
       </c>
       <c r="D99" s="53" t="inlineStr">
         <is>
-          <t>livanov@draycottgx.com</t>
+          <t>l.ulrich@draycottgx.com</t>
         </is>
       </c>
       <c r="E99" s="38" t="inlineStr">
@@ -5806,12 +5918,12 @@
       </c>
       <c r="C100" s="41" t="inlineStr">
         <is>
-          <t>Jamal Booker</t>
+          <t>Kofi Kapoor</t>
         </is>
       </c>
       <c r="D100" s="49" t="inlineStr">
         <is>
-          <t>jbooker@elmwoodbio.com</t>
+          <t>k.kapoor@elmwoodbio.com</t>
         </is>
       </c>
       <c r="E100" s="41" t="inlineStr">
@@ -5854,12 +5966,12 @@
       </c>
       <c r="C101" s="38" t="inlineStr">
         <is>
-          <t>Yuki Sato</t>
+          <t>Kai Volkov</t>
         </is>
       </c>
       <c r="D101" s="53" t="inlineStr">
         <is>
-          <t>ysato@ferncliffdx.com</t>
+          <t>k.volkov@ferncliffdx.com</t>
         </is>
       </c>
       <c r="E101" s="38" t="inlineStr">
@@ -5902,12 +6014,12 @@
       </c>
       <c r="C102" s="41" t="inlineStr">
         <is>
-          <t>Amir Hassan</t>
+          <t>Nia Kallas</t>
         </is>
       </c>
       <c r="D102" s="49" t="inlineStr">
         <is>
-          <t>ahassan@gairlochanalytical.com</t>
+          <t>n.kallas@gairlochanalytical.com</t>
         </is>
       </c>
       <c r="E102" s="41" t="inlineStr">
@@ -5950,12 +6062,12 @@
       </c>
       <c r="C103" s="38" t="inlineStr">
         <is>
-          <t>Priyanka Iyer</t>
+          <t>Gustav Tanaka</t>
         </is>
       </c>
       <c r="D103" s="53" t="inlineStr">
         <is>
-          <t>piyer@harborlightbio.com</t>
+          <t>g.tanaka@harborlightbio.com</t>
         </is>
       </c>
       <c r="E103" s="38" t="inlineStr">
@@ -5998,12 +6110,12 @@
       </c>
       <c r="C104" s="41" t="inlineStr">
         <is>
-          <t>Nathan Osei</t>
+          <t>Esther Moreau</t>
         </is>
       </c>
       <c r="D104" s="49" t="inlineStr">
         <is>
-          <t>nosei@isleyreagents.com</t>
+          <t>e.moreau@isleyreagents.com</t>
         </is>
       </c>
       <c r="E104" s="41" t="inlineStr">
@@ -6046,12 +6158,12 @@
       </c>
       <c r="C105" s="38" t="inlineStr">
         <is>
-          <t>Kai Nakamura</t>
+          <t>Ishaan Marchetti</t>
         </is>
       </c>
       <c r="D105" s="53" t="inlineStr">
         <is>
-          <t>knakamura@jerbrookdx.com</t>
+          <t>i.marchetti@jerbrookdx.com</t>
         </is>
       </c>
       <c r="E105" s="38" t="inlineStr">
@@ -6094,12 +6206,12 @@
       </c>
       <c r="C106" s="41" t="inlineStr">
         <is>
-          <t>Farah Al-Sayed</t>
+          <t>Farah Nikolic</t>
         </is>
       </c>
       <c r="D106" s="49" t="inlineStr">
         <is>
-          <t>falsayed@kilburnmol.com</t>
+          <t>f.nikolic@kilburnmol.com</t>
         </is>
       </c>
       <c r="E106" s="41" t="inlineStr">
@@ -6142,12 +6254,12 @@
       </c>
       <c r="C107" s="38" t="inlineStr">
         <is>
-          <t>Ingrid Larsen</t>
+          <t>Idris Lundgren</t>
         </is>
       </c>
       <c r="D107" s="53" t="inlineStr">
         <is>
-          <t>ilarsen@ledburyassays.com</t>
+          <t>i.lundgren@ledburyassays.com</t>
         </is>
       </c>
       <c r="E107" s="38" t="inlineStr">
@@ -6190,12 +6302,12 @@
       </c>
       <c r="C108" s="41" t="inlineStr">
         <is>
-          <t>Rangi Osei</t>
+          <t>Oscar Kowalski</t>
         </is>
       </c>
       <c r="D108" s="49" t="inlineStr">
         <is>
-          <t>rosei@meritbio.com</t>
+          <t>o.kowalski@meritbio.com</t>
         </is>
       </c>
       <c r="E108" s="41" t="inlineStr">
@@ -6238,12 +6350,12 @@
       </c>
       <c r="C109" s="38" t="inlineStr">
         <is>
-          <t>Marcus Weiss</t>
+          <t>Elena Radu</t>
         </is>
       </c>
       <c r="D109" s="53" t="inlineStr">
         <is>
-          <t>mweiss@newburyinst.com</t>
+          <t>e.radu@newburyinst.com</t>
         </is>
       </c>
       <c r="E109" s="38" t="inlineStr">
@@ -6286,12 +6398,12 @@
       </c>
       <c r="C110" s="41" t="inlineStr">
         <is>
-          <t>Aisha Khan</t>
+          <t>Fiorella Moreau</t>
         </is>
       </c>
       <c r="D110" s="49" t="inlineStr">
         <is>
-          <t>akhan@orleansgx.com</t>
+          <t>f.moreau@orleansgx.com</t>
         </is>
       </c>
       <c r="E110" s="41" t="inlineStr">
@@ -6334,12 +6446,12 @@
       </c>
       <c r="C111" s="38" t="inlineStr">
         <is>
-          <t>Neha Kapoor</t>
+          <t>Callum Eriksson</t>
         </is>
       </c>
       <c r="D111" s="53" t="inlineStr">
         <is>
-          <t>nkapoor@pembertondx.com</t>
+          <t>c.eriksson@pembertondx.com</t>
         </is>
       </c>
       <c r="E111" s="38" t="inlineStr">
@@ -6382,12 +6494,12 @@
       </c>
       <c r="C112" s="41" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Hana Nikolic</t>
         </is>
       </c>
       <c r="D112" s="49" t="inlineStr">
         <is>
-          <t>s.marchetti@quentonbiolabs.com</t>
+          <t>h.nikolic@quentonbiolabs.com</t>
         </is>
       </c>
       <c r="E112" s="41" t="inlineStr">
@@ -6430,12 +6542,12 @@
       </c>
       <c r="C113" s="38" t="inlineStr">
         <is>
-          <t>Ivaan Sharma</t>
+          <t>Priyanka Lindqvist</t>
         </is>
       </c>
       <c r="D113" s="53" t="inlineStr">
         <is>
-          <t>isharma@ramseyanalytical.com</t>
+          <t>p.lindqvist@ramseyanalytical.com</t>
         </is>
       </c>
       <c r="E113" s="38" t="inlineStr">
@@ -6478,12 +6590,12 @@
       </c>
       <c r="C114" s="41" t="inlineStr">
         <is>
-          <t>Richard Ainsley</t>
+          <t>Edvard Booker</t>
         </is>
       </c>
       <c r="D114" s="49" t="inlineStr">
         <is>
-          <t>richard.ainsley@sutherlandreagents.com</t>
+          <t>e.booker@sutherlandreagents.com</t>
         </is>
       </c>
       <c r="E114" s="41" t="inlineStr">
@@ -6526,12 +6638,12 @@
       </c>
       <c r="C115" s="38" t="inlineStr">
         <is>
-          <t>Elena Cortez</t>
+          <t>Yuki Quintero</t>
         </is>
       </c>
       <c r="D115" s="53" t="inlineStr">
         <is>
-          <t>ecortez@trellismol.com</t>
+          <t>y.quintero@trellismol.com</t>
         </is>
       </c>
       <c r="E115" s="38" t="inlineStr">
@@ -6574,12 +6686,12 @@
       </c>
       <c r="C116" s="41" t="inlineStr">
         <is>
-          <t>Diya Chandra</t>
+          <t>Rangi Rowe</t>
         </is>
       </c>
       <c r="D116" s="49" t="inlineStr">
         <is>
-          <t>dchandra@underhillbio.com</t>
+          <t>r.rowe@underhillbio.com</t>
         </is>
       </c>
       <c r="E116" s="41" t="inlineStr">
@@ -6622,12 +6734,12 @@
       </c>
       <c r="C117" s="38" t="inlineStr">
         <is>
-          <t>Klaus Baumann</t>
+          <t>Aroha Ulrich</t>
         </is>
       </c>
       <c r="D117" s="53" t="inlineStr">
         <is>
-          <t>kbaumann@veronaassays.com</t>
+          <t>a.ulrich@veronaassays.com</t>
         </is>
       </c>
       <c r="E117" s="38" t="inlineStr">
@@ -6670,12 +6782,12 @@
       </c>
       <c r="C118" s="41" t="inlineStr">
         <is>
-          <t>Ana Silva</t>
+          <t>Meredith Isaev</t>
         </is>
       </c>
       <c r="D118" s="49" t="inlineStr">
         <is>
-          <t>asilva@whitfielddx.com</t>
+          <t>m.isaev@whitfielddx.com</t>
         </is>
       </c>
       <c r="E118" s="41" t="inlineStr">
@@ -6718,12 +6830,12 @@
       </c>
       <c r="C119" s="38" t="inlineStr">
         <is>
-          <t>Chen Wei</t>
+          <t>Ingrid Isaev</t>
         </is>
       </c>
       <c r="D119" s="53" t="inlineStr">
         <is>
-          <t>cwei@xantheinst.com</t>
+          <t>i.isaev@xantheinst.com</t>
         </is>
       </c>
       <c r="E119" s="38" t="inlineStr">
@@ -6766,12 +6878,12 @@
       </c>
       <c r="C120" s="41" t="inlineStr">
         <is>
-          <t>Owen Booker</t>
+          <t>Lucas Tanaka</t>
         </is>
       </c>
       <c r="D120" s="49" t="inlineStr">
         <is>
-          <t>obooker@yorktownbio.com</t>
+          <t>l.tanaka@yorktownbio.com</t>
         </is>
       </c>
       <c r="E120" s="41" t="inlineStr">
@@ -6814,12 +6926,12 @@
       </c>
       <c r="C121" s="38" t="inlineStr">
         <is>
-          <t>Petra Volkov</t>
+          <t>Sofia Chiu</t>
         </is>
       </c>
       <c r="D121" s="53" t="inlineStr">
         <is>
-          <t>pvolkov@zephyrgx.com</t>
+          <t>s.chiu@zephyrgx.com</t>
         </is>
       </c>
       <c r="E121" s="38" t="inlineStr">
@@ -6862,12 +6974,12 @@
       </c>
       <c r="C122" s="41" t="inlineStr">
         <is>
-          <t>Amir Hassan</t>
+          <t>Kai Quintero</t>
         </is>
       </c>
       <c r="D122" s="49" t="inlineStr">
         <is>
-          <t>ahassan@aldermandx.com</t>
+          <t>k.quintero@aldermandx.com</t>
         </is>
       </c>
       <c r="E122" s="41" t="inlineStr">
@@ -6910,12 +7022,12 @@
       </c>
       <c r="C123" s="38" t="inlineStr">
         <is>
-          <t>Malia Kekoa</t>
+          <t>Klaus Marchand</t>
         </is>
       </c>
       <c r="D123" s="53" t="inlineStr">
         <is>
-          <t>mkekoa@bosworthbio.com</t>
+          <t>k.marchand@bosworthbio.com</t>
         </is>
       </c>
       <c r="E123" s="38" t="inlineStr">
@@ -6958,12 +7070,12 @@
       </c>
       <c r="C124" s="41" t="inlineStr">
         <is>
-          <t>Aditi Rao</t>
+          <t>Keiko Kapoor</t>
         </is>
       </c>
       <c r="D124" s="49" t="inlineStr">
         <is>
-          <t>arao@colvinreagents.com</t>
+          <t>k.kapoor@colvinreagents.com</t>
         </is>
       </c>
       <c r="E124" s="41" t="inlineStr">
@@ -7006,12 +7118,12 @@
       </c>
       <c r="C125" s="38" t="inlineStr">
         <is>
-          <t>Boris Sokolov</t>
+          <t>Selin Wisniewski</t>
         </is>
       </c>
       <c r="D125" s="53" t="inlineStr">
         <is>
-          <t>bsokolov@deerfieldmol.com</t>
+          <t>s.wisniewski@deerfieldmol.com</t>
         </is>
       </c>
       <c r="E125" s="38" t="inlineStr">
@@ -7054,12 +7166,12 @@
       </c>
       <c r="C126" s="41" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Owen Lundgren</t>
         </is>
       </c>
       <c r="D126" s="49" t="inlineStr">
         <is>
-          <t>rsharma@estwickinst.com</t>
+          <t>o.lundgren@estwickinst.com</t>
         </is>
       </c>
       <c r="E126" s="41" t="inlineStr">
@@ -7102,12 +7214,12 @@
       </c>
       <c r="C127" s="38" t="inlineStr">
         <is>
-          <t>Vikram Nair</t>
+          <t>Anika Janik</t>
         </is>
       </c>
       <c r="D127" s="53" t="inlineStr">
         <is>
-          <t>vnair@fairhavenanalytical.com</t>
+          <t>a.janik@fairhavenanalytical.com</t>
         </is>
       </c>
       <c r="E127" s="38" t="inlineStr">
@@ -7145,22 +7257,22 @@
       </c>
       <c r="B128" s="41" t="inlineStr">
         <is>
-          <t>Glenridge BioLabs</t>
+          <t>Halewood Diagnostics</t>
         </is>
       </c>
       <c r="C128" s="41" t="inlineStr">
         <is>
-          <t>Henry Beauchamp</t>
+          <t>Priyanka Radu</t>
         </is>
       </c>
       <c r="D128" s="49" t="inlineStr">
         <is>
-          <t>h.beauchamp2@glenridgebiolabs.com</t>
+          <t>p.radu@halewooddx.com</t>
         </is>
       </c>
       <c r="E128" s="41" t="inlineStr">
         <is>
-          <t>Inbound — Demo request</t>
+          <t>Webinar — Diagnostics ROI</t>
         </is>
       </c>
       <c r="F128" s="41" t="inlineStr">
@@ -7173,16 +7285,16 @@
       </c>
       <c r="H128" s="41" t="inlineStr">
         <is>
-          <t>Sun-Hi Park</t>
+          <t>Kenji Watanabe</t>
         </is>
       </c>
       <c r="I128" s="41" t="inlineStr">
         <is>
-          <t>Proposal</t>
+          <t>Qualification</t>
         </is>
       </c>
       <c r="J128" s="51" t="n">
-        <v>118000</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="129" ht="21" customHeight="1">
@@ -7193,44 +7305,44 @@
       </c>
       <c r="B129" s="38" t="inlineStr">
         <is>
-          <t>Halewood Diagnostics</t>
+          <t>Ivywood Assays</t>
         </is>
       </c>
       <c r="C129" s="38" t="inlineStr">
         <is>
-          <t>Zara Ahmed</t>
+          <t>Fiorella Eriksson</t>
         </is>
       </c>
       <c r="D129" s="53" t="inlineStr">
         <is>
-          <t>zahmed@halewooddx.com</t>
+          <t>f.eriksson@ivywoodassays.com</t>
         </is>
       </c>
       <c r="E129" s="38" t="inlineStr">
         <is>
-          <t>Webinar — Diagnostics ROI</t>
+          <t>Product trial — Website</t>
         </is>
       </c>
       <c r="F129" s="38" t="inlineStr">
         <is>
-          <t>Sales-Touched</t>
+          <t>Self-Serve Trial</t>
         </is>
       </c>
       <c r="G129" s="54" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="H129" s="38" t="inlineStr">
         <is>
-          <t>Kenji Watanabe</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="I129" s="38" t="inlineStr">
         <is>
-          <t>Qualification</t>
+          <t>Trial - Active</t>
         </is>
       </c>
       <c r="J129" s="55" t="n">
-        <v>46000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" ht="21" customHeight="1">
@@ -7241,27 +7353,27 @@
       </c>
       <c r="B130" s="41" t="inlineStr">
         <is>
-          <t>Ivywood Assays</t>
+          <t>Junction Reagents</t>
         </is>
       </c>
       <c r="C130" s="41" t="inlineStr">
         <is>
-          <t>Fatima Farouk</t>
+          <t>Petra Terzic</t>
         </is>
       </c>
       <c r="D130" s="49" t="inlineStr">
         <is>
-          <t>ffarouk@ivywoodassays.com</t>
+          <t>p.terzic@junctionreagents.com</t>
         </is>
       </c>
       <c r="E130" s="41" t="inlineStr">
         <is>
-          <t>Product trial — Website</t>
+          <t>Content download — Case Study</t>
         </is>
       </c>
       <c r="F130" s="41" t="inlineStr">
         <is>
-          <t>Self-Serve Trial</t>
+          <t>Sales-Touched</t>
         </is>
       </c>
       <c r="G130" s="50" t="n">
@@ -7269,16 +7381,16 @@
       </c>
       <c r="H130" s="41" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Erik Vaskovic</t>
         </is>
       </c>
       <c r="I130" s="41" t="inlineStr">
         <is>
-          <t>Trial - Active</t>
+          <t>Discovery</t>
         </is>
       </c>
       <c r="J130" s="51" t="n">
-        <v>0</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="131" ht="21" customHeight="1">
@@ -7289,22 +7401,22 @@
       </c>
       <c r="B131" s="38" t="inlineStr">
         <is>
-          <t>Junction Reagents</t>
+          <t>Keswick Genomics</t>
         </is>
       </c>
       <c r="C131" s="38" t="inlineStr">
         <is>
-          <t>Nathan Osei</t>
+          <t>Larisa Ashworth</t>
         </is>
       </c>
       <c r="D131" s="53" t="inlineStr">
         <is>
-          <t>nosei@junctionreagents.com</t>
+          <t>l.ashworth@keswickgx.com</t>
         </is>
       </c>
       <c r="E131" s="38" t="inlineStr">
         <is>
-          <t>Content download — Case Study</t>
+          <t>Analyst inquiry</t>
         </is>
       </c>
       <c r="F131" s="38" t="inlineStr">
@@ -7313,11 +7425,11 @@
         </is>
       </c>
       <c r="G131" s="54" t="n">
-        <v>45987</v>
+        <v>45988</v>
       </c>
       <c r="H131" s="38" t="inlineStr">
         <is>
-          <t>Erik Vaskovic</t>
+          <t>Marisol Aguirre</t>
         </is>
       </c>
       <c r="I131" s="38" t="inlineStr">
@@ -7326,7 +7438,7 @@
         </is>
       </c>
       <c r="J131" s="55" t="n">
-        <v>28000</v>
+        <v>79000</v>
       </c>
     </row>
     <row r="132" ht="21" customHeight="1">
@@ -7337,27 +7449,27 @@
       </c>
       <c r="B132" s="41" t="inlineStr">
         <is>
-          <t>Keswick Genomics</t>
+          <t>Lyndhurst Instruments</t>
         </is>
       </c>
       <c r="C132" s="41" t="inlineStr">
         <is>
-          <t>Anaya Patel</t>
+          <t>Wren Ibori</t>
         </is>
       </c>
       <c r="D132" s="49" t="inlineStr">
         <is>
-          <t>apatel@keswickgx.com</t>
+          <t>w.ibori@lyndhurstinst.com</t>
         </is>
       </c>
       <c r="E132" s="41" t="inlineStr">
         <is>
-          <t>Analyst inquiry</t>
+          <t>Product trial — Google Ad</t>
         </is>
       </c>
       <c r="F132" s="41" t="inlineStr">
         <is>
-          <t>Sales-Touched</t>
+          <t>Self-Serve Trial</t>
         </is>
       </c>
       <c r="G132" s="50" t="n">
@@ -7365,16 +7477,16 @@
       </c>
       <c r="H132" s="41" t="inlineStr">
         <is>
-          <t>Marisol Aguirre</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="I132" s="41" t="inlineStr">
         <is>
-          <t>Discovery</t>
+          <t>Trial - Active</t>
         </is>
       </c>
       <c r="J132" s="51" t="n">
-        <v>79000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" ht="21" customHeight="1">
@@ -7385,44 +7497,44 @@
       </c>
       <c r="B133" s="38" t="inlineStr">
         <is>
-          <t>Lyndhurst Instruments</t>
+          <t>Marston Bio</t>
         </is>
       </c>
       <c r="C133" s="38" t="inlineStr">
         <is>
-          <t>Ishaan Verma</t>
+          <t>Sofia Iyer</t>
         </is>
       </c>
       <c r="D133" s="53" t="inlineStr">
         <is>
-          <t>iverma@lyndhurstinst.com</t>
+          <t>s.iyer@marstonbio.com</t>
         </is>
       </c>
       <c r="E133" s="38" t="inlineStr">
         <is>
-          <t>Product trial — Google Ad</t>
+          <t>Conference — AACC 2025</t>
         </is>
       </c>
       <c r="F133" s="38" t="inlineStr">
         <is>
-          <t>Self-Serve Trial</t>
+          <t>Sales-Touched</t>
         </is>
       </c>
       <c r="G133" s="54" t="n">
-        <v>45988</v>
+        <v>45989</v>
       </c>
       <c r="H133" s="38" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Tomasz Bergstrom</t>
         </is>
       </c>
       <c r="I133" s="38" t="inlineStr">
         <is>
-          <t>Trial - Active</t>
+          <t>Qualification</t>
         </is>
       </c>
       <c r="J133" s="55" t="n">
-        <v>0</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="134" ht="21" customHeight="1">
@@ -7433,22 +7545,22 @@
       </c>
       <c r="B134" s="41" t="inlineStr">
         <is>
-          <t>Marston Bio</t>
+          <t>Oakenwood Diagnostics</t>
         </is>
       </c>
       <c r="C134" s="41" t="inlineStr">
         <is>
-          <t>Kenji Nakamura</t>
+          <t>Larisa Tanaka</t>
         </is>
       </c>
       <c r="D134" s="49" t="inlineStr">
         <is>
-          <t>knakamura@marstonbio.com</t>
+          <t>l.tanaka@oakenwooddx.com</t>
         </is>
       </c>
       <c r="E134" s="41" t="inlineStr">
         <is>
-          <t>Conference — AACC 2025</t>
+          <t>Referral — Partner</t>
         </is>
       </c>
       <c r="F134" s="41" t="inlineStr">
@@ -7461,16 +7573,16 @@
       </c>
       <c r="H134" s="41" t="inlineStr">
         <is>
-          <t>Tomasz Bergstrom</t>
+          <t>Rachel Ohaeri</t>
         </is>
       </c>
       <c r="I134" s="41" t="inlineStr">
         <is>
-          <t>Qualification</t>
+          <t>Discovery</t>
         </is>
       </c>
       <c r="J134" s="51" t="n">
-        <v>56000</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="135" ht="21" customHeight="1">
@@ -7481,44 +7593,44 @@
       </c>
       <c r="B135" s="38" t="inlineStr">
         <is>
-          <t>Oakenwood Diagnostics</t>
+          <t>Pentworth Molecular</t>
         </is>
       </c>
       <c r="C135" s="38" t="inlineStr">
         <is>
-          <t>Rangi Osei</t>
+          <t>Dahlia Okafor</t>
         </is>
       </c>
       <c r="D135" s="53" t="inlineStr">
         <is>
-          <t>rosei@oakenwooddx.com</t>
+          <t>d.okafor@pentworthmol.com</t>
         </is>
       </c>
       <c r="E135" s="38" t="inlineStr">
         <is>
-          <t>Referral — Partner</t>
+          <t>Product trial — Free tier</t>
         </is>
       </c>
       <c r="F135" s="38" t="inlineStr">
         <is>
-          <t>Sales-Touched</t>
+          <t>Self-Serve Trial</t>
         </is>
       </c>
       <c r="G135" s="54" t="n">
-        <v>45989</v>
+        <v>45990</v>
       </c>
       <c r="H135" s="38" t="inlineStr">
         <is>
-          <t>Rachel Ohaeri</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="I135" s="38" t="inlineStr">
         <is>
-          <t>Discovery</t>
+          <t>Trial - Active</t>
         </is>
       </c>
       <c r="J135" s="55" t="n">
-        <v>42000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" ht="21" customHeight="1">
@@ -7529,27 +7641,27 @@
       </c>
       <c r="B136" s="41" t="inlineStr">
         <is>
-          <t>Pentworth Molecular</t>
+          <t>Quaywater BioLabs</t>
         </is>
       </c>
       <c r="C136" s="41" t="inlineStr">
         <is>
-          <t>Naveen Chandra</t>
+          <t>Owen Weiss</t>
         </is>
       </c>
       <c r="D136" s="49" t="inlineStr">
         <is>
-          <t>nchandra@pentworthmol.com</t>
+          <t>o.weiss@quaywaterbiolabs.com</t>
         </is>
       </c>
       <c r="E136" s="41" t="inlineStr">
         <is>
-          <t>Product trial — Free tier</t>
+          <t>Warm intro — Advisor</t>
         </is>
       </c>
       <c r="F136" s="41" t="inlineStr">
         <is>
-          <t>Self-Serve Trial</t>
+          <t>Sales-Touched</t>
         </is>
       </c>
       <c r="G136" s="50" t="n">
@@ -7557,16 +7669,16 @@
       </c>
       <c r="H136" s="41" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Devon Blackthorne</t>
         </is>
       </c>
       <c r="I136" s="41" t="inlineStr">
         <is>
-          <t>Trial - Active</t>
+          <t>Proposal</t>
         </is>
       </c>
       <c r="J136" s="51" t="n">
-        <v>0</v>
+        <v>95500</v>
       </c>
     </row>
     <row r="137" ht="21" customHeight="1">
@@ -7577,22 +7689,22 @@
       </c>
       <c r="B137" s="38" t="inlineStr">
         <is>
-          <t>Quaywater BioLabs</t>
+          <t>Rowton Reagents</t>
         </is>
       </c>
       <c r="C137" s="38" t="inlineStr">
         <is>
-          <t>Priya Menon</t>
+          <t>Chen Tanaka</t>
         </is>
       </c>
       <c r="D137" s="53" t="inlineStr">
         <is>
-          <t>pmenon@quaywaterbiolabs.com</t>
+          <t>c.tanaka@rowtonreagents.com</t>
         </is>
       </c>
       <c r="E137" s="38" t="inlineStr">
         <is>
-          <t>Warm intro — Advisor</t>
+          <t>Outbound — SDR sequence</t>
         </is>
       </c>
       <c r="F137" s="38" t="inlineStr">
@@ -7601,20 +7713,20 @@
         </is>
       </c>
       <c r="G137" s="54" t="n">
-        <v>45990</v>
+        <v>45991</v>
       </c>
       <c r="H137" s="38" t="inlineStr">
         <is>
-          <t>Devon Blackthorne</t>
+          <t>Sun-Hi Park</t>
         </is>
       </c>
       <c r="I137" s="38" t="inlineStr">
         <is>
-          <t>Proposal</t>
+          <t>Discovery</t>
         </is>
       </c>
       <c r="J137" s="55" t="n">
-        <v>95500</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="138" ht="21" customHeight="1">
@@ -7625,22 +7737,22 @@
       </c>
       <c r="B138" s="41" t="inlineStr">
         <is>
-          <t>Rowton Reagents</t>
+          <t>Tavistock Assays</t>
         </is>
       </c>
       <c r="C138" s="41" t="inlineStr">
         <is>
-          <t>Elena Baumann</t>
+          <t>Tariq Isaev</t>
         </is>
       </c>
       <c r="D138" s="49" t="inlineStr">
         <is>
-          <t>ebaumann@rowtonreagents.com</t>
+          <t>t.isaev@tavistockassays.com</t>
         </is>
       </c>
       <c r="E138" s="41" t="inlineStr">
         <is>
-          <t>Outbound — SDR sequence</t>
+          <t>LinkedIn — Sponsored Content</t>
         </is>
       </c>
       <c r="F138" s="41" t="inlineStr">
@@ -7653,16 +7765,16 @@
       </c>
       <c r="H138" s="41" t="inlineStr">
         <is>
-          <t>Sun-Hi Park</t>
+          <t>Kenji Watanabe</t>
         </is>
       </c>
       <c r="I138" s="41" t="inlineStr">
         <is>
-          <t>Discovery</t>
+          <t>Qualification</t>
         </is>
       </c>
       <c r="J138" s="51" t="n">
-        <v>36000</v>
+        <v>63500</v>
       </c>
     </row>
     <row r="139" ht="21" customHeight="1">
@@ -7673,44 +7785,44 @@
       </c>
       <c r="B139" s="38" t="inlineStr">
         <is>
-          <t>Tavistock Assays</t>
+          <t>Uxbridge Genomics</t>
         </is>
       </c>
       <c r="C139" s="38" t="inlineStr">
         <is>
-          <t>Sanjay Krishnamurthy</t>
+          <t>Kofi Chiu</t>
         </is>
       </c>
       <c r="D139" s="53" t="inlineStr">
         <is>
-          <t>s.krishnamurthy@tavistockassays.com</t>
+          <t>k.chiu@uxbridgegx.com</t>
         </is>
       </c>
       <c r="E139" s="38" t="inlineStr">
         <is>
-          <t>LinkedIn — Sponsored Content</t>
+          <t>Product trial — Website</t>
         </is>
       </c>
       <c r="F139" s="38" t="inlineStr">
         <is>
-          <t>Sales-Touched</t>
+          <t>Self-Serve Trial</t>
         </is>
       </c>
       <c r="G139" s="54" t="n">
-        <v>45991</v>
+        <v>45992</v>
       </c>
       <c r="H139" s="38" t="inlineStr">
         <is>
-          <t>Kenji Watanabe</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="I139" s="38" t="inlineStr">
         <is>
-          <t>Qualification</t>
+          <t>Trial - Active</t>
         </is>
       </c>
       <c r="J139" s="55" t="n">
-        <v>63500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" ht="21" customHeight="1">
@@ -7721,27 +7833,27 @@
       </c>
       <c r="B140" s="41" t="inlineStr">
         <is>
-          <t>Uxbridge Genomics</t>
+          <t>Vallon Instruments</t>
         </is>
       </c>
       <c r="C140" s="41" t="inlineStr">
         <is>
-          <t>Aroha Manaia</t>
+          <t>Yasmin Yilmaz</t>
         </is>
       </c>
       <c r="D140" s="49" t="inlineStr">
         <is>
-          <t>amanaia@uxbridgegx.com</t>
+          <t>y.yilmaz@valloninst.com</t>
         </is>
       </c>
       <c r="E140" s="41" t="inlineStr">
         <is>
-          <t>Product trial — Website</t>
+          <t>Conference — Bio-IT World</t>
         </is>
       </c>
       <c r="F140" s="41" t="inlineStr">
         <is>
-          <t>Self-Serve Trial</t>
+          <t>Sales-Touched</t>
         </is>
       </c>
       <c r="G140" s="50" t="n">
@@ -7749,16 +7861,16 @@
       </c>
       <c r="H140" s="41" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Erik Vaskovic</t>
         </is>
       </c>
       <c r="I140" s="41" t="inlineStr">
         <is>
-          <t>Trial - Active</t>
+          <t>Discovery</t>
         </is>
       </c>
       <c r="J140" s="51" t="n">
-        <v>0</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="141" ht="21" customHeight="1">
@@ -7769,27 +7881,27 @@
       </c>
       <c r="B141" s="38" t="inlineStr">
         <is>
-          <t>Vallon Instruments</t>
+          <t>Wintergreen BioScience</t>
         </is>
       </c>
       <c r="C141" s="38" t="inlineStr">
         <is>
-          <t>Amelia Rowe</t>
+          <t>Chen Quintero</t>
         </is>
       </c>
       <c r="D141" s="53" t="inlineStr">
         <is>
-          <t>amelia.rowe@valloninst.com</t>
+          <t>c.quintero@wintergreenbio.com</t>
         </is>
       </c>
       <c r="E141" s="38" t="inlineStr">
         <is>
-          <t>Conference — Bio-IT World</t>
+          <t>Product trial — Website</t>
         </is>
       </c>
       <c r="F141" s="38" t="inlineStr">
         <is>
-          <t>Sales-Touched</t>
+          <t>Self-Serve Trial</t>
         </is>
       </c>
       <c r="G141" s="54" t="n">
@@ -7797,16 +7909,16 @@
       </c>
       <c r="H141" s="38" t="inlineStr">
         <is>
-          <t>Erik Vaskovic</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="I141" s="38" t="inlineStr">
         <is>
-          <t>Discovery</t>
+          <t>Trial - Active</t>
         </is>
       </c>
       <c r="J141" s="55" t="n">
-        <v>48000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" ht="21" customHeight="1">
@@ -7817,44 +7929,44 @@
       </c>
       <c r="B142" s="41" t="inlineStr">
         <is>
-          <t>Wintergreen BioScience</t>
+          <t>Yardsley Analytical</t>
         </is>
       </c>
       <c r="C142" s="41" t="inlineStr">
         <is>
-          <t>Devon Cabrera</t>
+          <t>Grace Ulrich</t>
         </is>
       </c>
       <c r="D142" s="49" t="inlineStr">
         <is>
-          <t>dcabrera@wintergreenbio.com</t>
+          <t>g.ulrich@yardsleyanalytical.com</t>
         </is>
       </c>
       <c r="E142" s="41" t="inlineStr">
         <is>
-          <t>Product trial — Website</t>
+          <t>Inbound — RFP</t>
         </is>
       </c>
       <c r="F142" s="41" t="inlineStr">
         <is>
-          <t>Self-Serve Trial</t>
+          <t>Sales-Touched</t>
         </is>
       </c>
       <c r="G142" s="50" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="H142" s="41" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Tomasz Bergstrom</t>
         </is>
       </c>
       <c r="I142" s="41" t="inlineStr">
         <is>
-          <t>Trial - Active</t>
+          <t>Proposal</t>
         </is>
       </c>
       <c r="J142" s="51" t="n">
-        <v>0</v>
+        <v>134500</v>
       </c>
     </row>
     <row r="143" ht="21" customHeight="1">
@@ -7865,27 +7977,27 @@
       </c>
       <c r="B143" s="38" t="inlineStr">
         <is>
-          <t>Yardsley Analytical</t>
+          <t>Zenith Bio</t>
         </is>
       </c>
       <c r="C143" s="38" t="inlineStr">
         <is>
-          <t>Nikolai Petrov</t>
+          <t>Idris Verma</t>
         </is>
       </c>
       <c r="D143" s="53" t="inlineStr">
         <is>
-          <t>npetrov@yardsleyanalytical.com</t>
+          <t>i.verma@zenithbio.com</t>
         </is>
       </c>
       <c r="E143" s="38" t="inlineStr">
         <is>
-          <t>Inbound — RFP</t>
+          <t>Product trial — Referral link</t>
         </is>
       </c>
       <c r="F143" s="38" t="inlineStr">
         <is>
-          <t>Sales-Touched</t>
+          <t>Self-Serve Trial</t>
         </is>
       </c>
       <c r="G143" s="54" t="n">
@@ -7893,16 +8005,16 @@
       </c>
       <c r="H143" s="38" t="inlineStr">
         <is>
-          <t>Tomasz Bergstrom</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="I143" s="38" t="inlineStr">
         <is>
-          <t>Proposal</t>
+          <t>Trial - Active</t>
         </is>
       </c>
       <c r="J143" s="55" t="n">
-        <v>134500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" ht="21" customHeight="1">
@@ -7913,44 +8025,44 @@
       </c>
       <c r="B144" s="41" t="inlineStr">
         <is>
-          <t>Zenith Bio</t>
+          <t>Bramford Scientific</t>
         </is>
       </c>
       <c r="C144" s="41" t="inlineStr">
         <is>
-          <t>Lena Ivanov</t>
+          <t>Alistair Ostrowski</t>
         </is>
       </c>
       <c r="D144" s="49" t="inlineStr">
         <is>
-          <t>livanov@zenithbio.com</t>
+          <t>a.ostrowski@bramfordsci.com</t>
         </is>
       </c>
       <c r="E144" s="41" t="inlineStr">
         <is>
-          <t>Product trial — Referral link</t>
+          <t>Content download — Whitepaper</t>
         </is>
       </c>
       <c r="F144" s="41" t="inlineStr">
         <is>
-          <t>Self-Serve Trial</t>
+          <t>Sales-Touched</t>
         </is>
       </c>
       <c r="G144" s="50" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="H144" s="41" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Rachel Ohaeri</t>
         </is>
       </c>
       <c r="I144" s="41" t="inlineStr">
         <is>
-          <t>Trial - Active</t>
+          <t>Discovery</t>
         </is>
       </c>
       <c r="J144" s="51" t="n">
-        <v>0</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="145" ht="21" customHeight="1">
@@ -7961,22 +8073,22 @@
       </c>
       <c r="B145" s="38" t="inlineStr">
         <is>
-          <t>Bramford Scientific</t>
+          <t>Everglade Diagnostics</t>
         </is>
       </c>
       <c r="C145" s="38" t="inlineStr">
         <is>
-          <t>Ananya Iyer</t>
+          <t>Paloma Booker</t>
         </is>
       </c>
       <c r="D145" s="53" t="inlineStr">
         <is>
-          <t>aiyer@bramfordsci.com</t>
+          <t>p.booker@everglade-dx.com</t>
         </is>
       </c>
       <c r="E145" s="38" t="inlineStr">
         <is>
-          <t>Content download — Whitepaper</t>
+          <t>Webinar — Q4 Genomics Series</t>
         </is>
       </c>
       <c r="F145" s="38" t="inlineStr">
@@ -7989,16 +8101,16 @@
       </c>
       <c r="H145" s="38" t="inlineStr">
         <is>
-          <t>Rachel Ohaeri</t>
+          <t>Devon Blackthorne</t>
         </is>
       </c>
       <c r="I145" s="38" t="inlineStr">
         <is>
-          <t>Discovery</t>
+          <t>Qualification</t>
         </is>
       </c>
       <c r="J145" s="55" t="n">
-        <v>31000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="146" ht="21" customHeight="1">
@@ -8009,44 +8121,44 @@
       </c>
       <c r="B146" s="41" t="inlineStr">
         <is>
-          <t>Everglade Diagnostics</t>
+          <t>Longacre Labs</t>
         </is>
       </c>
       <c r="C146" s="41" t="inlineStr">
         <is>
-          <t>Kai Nakamura</t>
+          <t>Vikram Ostrowski</t>
         </is>
       </c>
       <c r="D146" s="49" t="inlineStr">
         <is>
-          <t>knakamura@everglade-dx.com</t>
+          <t>v.ostrowski@longacrelabs.com</t>
         </is>
       </c>
       <c r="E146" s="41" t="inlineStr">
         <is>
-          <t>Webinar — Q4 Genomics Series</t>
+          <t>Product trial — Google Ad</t>
         </is>
       </c>
       <c r="F146" s="41" t="inlineStr">
         <is>
-          <t>Sales-Touched</t>
+          <t>Self-Serve Trial</t>
         </is>
       </c>
       <c r="G146" s="50" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="H146" s="41" t="inlineStr">
         <is>
-          <t>Devon Blackthorne</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="I146" s="41" t="inlineStr">
         <is>
-          <t>Qualification</t>
+          <t>Trial - Active</t>
         </is>
       </c>
       <c r="J146" s="51" t="n">
-        <v>52000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" ht="21" customHeight="1">
@@ -8057,27 +8169,27 @@
       </c>
       <c r="B147" s="38" t="inlineStr">
         <is>
-          <t>Longacre Labs</t>
+          <t>Highfield Instruments</t>
         </is>
       </c>
       <c r="C147" s="38" t="inlineStr">
         <is>
-          <t>Anika Menon</t>
+          <t>Nathan Castellanos</t>
         </is>
       </c>
       <c r="D147" s="53" t="inlineStr">
         <is>
-          <t>amenon@longacrelabs.com</t>
+          <t>n.castellanos@highfieldinst.com</t>
         </is>
       </c>
       <c r="E147" s="38" t="inlineStr">
         <is>
-          <t>Product trial — Google Ad</t>
+          <t>Referral — Existing client</t>
         </is>
       </c>
       <c r="F147" s="38" t="inlineStr">
         <is>
-          <t>Self-Serve Trial</t>
+          <t>Sales-Touched</t>
         </is>
       </c>
       <c r="G147" s="54" t="n">
@@ -8085,16 +8197,16 @@
       </c>
       <c r="H147" s="38" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Sun-Hi Park</t>
         </is>
       </c>
       <c r="I147" s="38" t="inlineStr">
         <is>
-          <t>Trial - Active</t>
+          <t>Discovery</t>
         </is>
       </c>
       <c r="J147" s="55" t="n">
-        <v>0</v>
+        <v>57500</v>
       </c>
     </row>
     <row r="148" ht="21" customHeight="1">
@@ -8105,22 +8217,22 @@
       </c>
       <c r="B148" s="41" t="inlineStr">
         <is>
-          <t>Highfield Instruments</t>
+          <t>Hallmark Molecular</t>
         </is>
       </c>
       <c r="C148" s="41" t="inlineStr">
         <is>
-          <t>Aarav Bhatt</t>
+          <t>Amelia Moreau</t>
         </is>
       </c>
       <c r="D148" s="49" t="inlineStr">
         <is>
-          <t>abhatt@highfieldinst.com</t>
+          <t>a.moreau@hallmarkmol.com</t>
         </is>
       </c>
       <c r="E148" s="41" t="inlineStr">
         <is>
-          <t>Referral — Existing client</t>
+          <t>Analyst inquiry</t>
         </is>
       </c>
       <c r="F148" s="41" t="inlineStr">
@@ -8133,16 +8245,16 @@
       </c>
       <c r="H148" s="41" t="inlineStr">
         <is>
-          <t>Sun-Hi Park</t>
+          <t>Kenji Watanabe</t>
         </is>
       </c>
       <c r="I148" s="41" t="inlineStr">
         <is>
-          <t>Discovery</t>
+          <t>Proposal</t>
         </is>
       </c>
       <c r="J148" s="51" t="n">
-        <v>57500</v>
+        <v>107000</v>
       </c>
     </row>
     <row r="149" ht="21" customHeight="1">
@@ -8153,44 +8265,44 @@
       </c>
       <c r="B149" s="38" t="inlineStr">
         <is>
-          <t>Hallmark Molecular</t>
+          <t>Palladium Assays</t>
         </is>
       </c>
       <c r="C149" s="38" t="inlineStr">
         <is>
-          <t>Yuki Sato</t>
+          <t>Ximena Nowak</t>
         </is>
       </c>
       <c r="D149" s="53" t="inlineStr">
         <is>
-          <t>ysato@hallmarkmol.com</t>
+          <t>x.nowak@palladiumassays.com</t>
         </is>
       </c>
       <c r="E149" s="38" t="inlineStr">
         <is>
-          <t>Analyst inquiry</t>
+          <t>Product trial — Free tier</t>
         </is>
       </c>
       <c r="F149" s="38" t="inlineStr">
         <is>
-          <t>Sales-Touched</t>
+          <t>Self-Serve Trial</t>
         </is>
       </c>
       <c r="G149" s="54" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="H149" s="38" t="inlineStr">
         <is>
-          <t>Kenji Watanabe</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="I149" s="38" t="inlineStr">
         <is>
-          <t>Proposal</t>
+          <t>Trial - Lapsed</t>
         </is>
       </c>
       <c r="J149" s="55" t="n">
-        <v>107000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" ht="21" customHeight="1">
@@ -8201,27 +8313,27 @@
       </c>
       <c r="B150" s="41" t="inlineStr">
         <is>
-          <t>Palladium Assays</t>
+          <t>Coastwise Reagents</t>
         </is>
       </c>
       <c r="C150" s="41" t="inlineStr">
         <is>
-          <t>Jamal Booker</t>
+          <t>Torsten Wei</t>
         </is>
       </c>
       <c r="D150" s="49" t="inlineStr">
         <is>
-          <t>jbooker@palladiumassays.com</t>
+          <t>t.wei@coastwisereagents.com</t>
         </is>
       </c>
       <c r="E150" s="41" t="inlineStr">
         <is>
-          <t>Product trial — Free tier</t>
+          <t>Outbound — SDR sequence</t>
         </is>
       </c>
       <c r="F150" s="41" t="inlineStr">
         <is>
-          <t>Self-Serve Trial</t>
+          <t>Sales-Touched</t>
         </is>
       </c>
       <c r="G150" s="50" t="n">
@@ -8229,16 +8341,16 @@
       </c>
       <c r="H150" s="41" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Erik Vaskovic</t>
         </is>
       </c>
       <c r="I150" s="41" t="inlineStr">
         <is>
-          <t>Trial - Lapsed</t>
+          <t>Qualification</t>
         </is>
       </c>
       <c r="J150" s="51" t="n">
-        <v>0</v>
+        <v>38000</v>
       </c>
     </row>
     <row r="151" ht="21" customHeight="1">
@@ -8249,44 +8361,44 @@
       </c>
       <c r="B151" s="38" t="inlineStr">
         <is>
-          <t>Coastwise Reagents</t>
+          <t>Nettleford Bio</t>
         </is>
       </c>
       <c r="C151" s="38" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Boris Sato</t>
         </is>
       </c>
       <c r="D151" s="53" t="inlineStr">
         <is>
-          <t>s.marchetti@coastwisereagents.com</t>
+          <t>b.sato@nettlefordbio.com</t>
         </is>
       </c>
       <c r="E151" s="38" t="inlineStr">
         <is>
-          <t>Outbound — SDR sequence</t>
+          <t>Product trial — Website</t>
         </is>
       </c>
       <c r="F151" s="38" t="inlineStr">
         <is>
-          <t>Sales-Touched</t>
+          <t>Self-Serve Trial</t>
         </is>
       </c>
       <c r="G151" s="54" t="n">
-        <v>45996</v>
+        <v>45997</v>
       </c>
       <c r="H151" s="38" t="inlineStr">
         <is>
-          <t>Erik Vaskovic</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="I151" s="38" t="inlineStr">
         <is>
-          <t>Qualification</t>
+          <t>Trial - Active</t>
         </is>
       </c>
       <c r="J151" s="55" t="n">
-        <v>38000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" ht="21" customHeight="1">
@@ -8297,27 +8409,27 @@
       </c>
       <c r="B152" s="41" t="inlineStr">
         <is>
-          <t>Nettleford Bio</t>
+          <t>Kadence Diagnostics</t>
         </is>
       </c>
       <c r="C152" s="41" t="inlineStr">
         <is>
-          <t>Ivaan Sharma</t>
+          <t>Fatima Hoffmann</t>
         </is>
       </c>
       <c r="D152" s="49" t="inlineStr">
         <is>
-          <t>isharma@nettlefordbio.com</t>
+          <t>f.hoffmann@kadencedx.com</t>
         </is>
       </c>
       <c r="E152" s="41" t="inlineStr">
         <is>
-          <t>Product trial — Website</t>
+          <t>Conference — MEDICA 2025</t>
         </is>
       </c>
       <c r="F152" s="41" t="inlineStr">
         <is>
-          <t>Self-Serve Trial</t>
+          <t>Sales-Touched</t>
         </is>
       </c>
       <c r="G152" s="50" t="n">
@@ -8325,16 +8437,16 @@
       </c>
       <c r="H152" s="41" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Marisol Aguirre</t>
         </is>
       </c>
       <c r="I152" s="41" t="inlineStr">
         <is>
-          <t>Trial - Active</t>
+          <t>Discovery</t>
         </is>
       </c>
       <c r="J152" s="51" t="n">
-        <v>0</v>
+        <v>44500</v>
       </c>
     </row>
     <row r="153" ht="21" customHeight="1">
@@ -8345,22 +8457,22 @@
       </c>
       <c r="B153" s="38" t="inlineStr">
         <is>
-          <t>Kadence Diagnostics</t>
+          <t>Ashland Genomics</t>
         </is>
       </c>
       <c r="C153" s="38" t="inlineStr">
         <is>
-          <t>Farah Al-Sayed</t>
+          <t>Sanjay Dahl</t>
         </is>
       </c>
       <c r="D153" s="53" t="inlineStr">
         <is>
-          <t>falsayed@kadencedx.com</t>
+          <t>s.dahl@ashlandgx.com</t>
         </is>
       </c>
       <c r="E153" s="38" t="inlineStr">
         <is>
-          <t>Conference — MEDICA 2025</t>
+          <t>LinkedIn — Sponsored Content</t>
         </is>
       </c>
       <c r="F153" s="38" t="inlineStr">
@@ -8369,20 +8481,20 @@
         </is>
       </c>
       <c r="G153" s="54" t="n">
-        <v>45997</v>
+        <v>45998</v>
       </c>
       <c r="H153" s="38" t="inlineStr">
         <is>
-          <t>Marisol Aguirre</t>
+          <t>Tomasz Bergstrom</t>
         </is>
       </c>
       <c r="I153" s="38" t="inlineStr">
         <is>
-          <t>Discovery</t>
+          <t>Nurture</t>
         </is>
       </c>
       <c r="J153" s="55" t="n">
-        <v>44500</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="154" ht="21" customHeight="1">
@@ -8393,27 +8505,27 @@
       </c>
       <c r="B154" s="41" t="inlineStr">
         <is>
-          <t>Ashland Genomics</t>
+          <t>Brixton Reagents</t>
         </is>
       </c>
       <c r="C154" s="41" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Amir Kapoor</t>
         </is>
       </c>
       <c r="D154" s="49" t="inlineStr">
         <is>
-          <t>rsharma@ashlandgx.com</t>
+          <t>a.kapoor@brixtonreagents.com</t>
         </is>
       </c>
       <c r="E154" s="41" t="inlineStr">
         <is>
-          <t>LinkedIn — Sponsored Content</t>
+          <t>Product trial — Organic search</t>
         </is>
       </c>
       <c r="F154" s="41" t="inlineStr">
         <is>
-          <t>Sales-Touched</t>
+          <t>Self-Serve Trial</t>
         </is>
       </c>
       <c r="G154" s="50" t="n">
@@ -8421,16 +8533,16 @@
       </c>
       <c r="H154" s="41" t="inlineStr">
         <is>
-          <t>Tomasz Bergstrom</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="I154" s="41" t="inlineStr">
         <is>
-          <t>Nurture</t>
+          <t>Trial - Active</t>
         </is>
       </c>
       <c r="J154" s="51" t="n">
-        <v>19500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" ht="21" customHeight="1">
@@ -8441,44 +8553,44 @@
       </c>
       <c r="B155" s="38" t="inlineStr">
         <is>
-          <t>Brixton Reagents</t>
+          <t>Willowmere Diagnostics</t>
         </is>
       </c>
       <c r="C155" s="38" t="inlineStr">
         <is>
-          <t>Chen Wei</t>
+          <t>Nikolai Radu</t>
         </is>
       </c>
       <c r="D155" s="53" t="inlineStr">
         <is>
-          <t>cwei@brixtonreagents.com</t>
+          <t>n.radu@willowmeredx.com</t>
         </is>
       </c>
       <c r="E155" s="38" t="inlineStr">
         <is>
-          <t>Product trial — Organic search</t>
+          <t>Warm intro — Advisor</t>
         </is>
       </c>
       <c r="F155" s="38" t="inlineStr">
         <is>
-          <t>Self-Serve Trial</t>
+          <t>Sales-Touched</t>
         </is>
       </c>
       <c r="G155" s="54" t="n">
-        <v>45998</v>
+        <v>45999</v>
       </c>
       <c r="H155" s="38" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Rachel Ohaeri</t>
         </is>
       </c>
       <c r="I155" s="38" t="inlineStr">
         <is>
-          <t>Trial - Active</t>
+          <t>Proposal</t>
         </is>
       </c>
       <c r="J155" s="55" t="n">
-        <v>0</v>
+        <v>128000</v>
       </c>
     </row>
     <row r="156" ht="21" customHeight="1">
@@ -8489,22 +8601,22 @@
       </c>
       <c r="B156" s="41" t="inlineStr">
         <is>
-          <t>Willowmere Diagnostics</t>
+          <t>Selby Instruments</t>
         </is>
       </c>
       <c r="C156" s="41" t="inlineStr">
         <is>
-          <t>Ingrid Larsen</t>
+          <t>Vera Zajac</t>
         </is>
       </c>
       <c r="D156" s="49" t="inlineStr">
         <is>
-          <t>ilarsen@willowmeredx.com</t>
+          <t>v.zajac@selbyinst.com</t>
         </is>
       </c>
       <c r="E156" s="41" t="inlineStr">
         <is>
-          <t>Warm intro — Advisor</t>
+          <t>Inbound — Demo request</t>
         </is>
       </c>
       <c r="F156" s="41" t="inlineStr">
@@ -8517,16 +8629,16 @@
       </c>
       <c r="H156" s="41" t="inlineStr">
         <is>
-          <t>Rachel Ohaeri</t>
+          <t>Devon Blackthorne</t>
         </is>
       </c>
       <c r="I156" s="41" t="inlineStr">
         <is>
-          <t>Proposal</t>
+          <t>Discovery</t>
         </is>
       </c>
       <c r="J156" s="51" t="n">
-        <v>128000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="157" ht="21" customHeight="1">
@@ -8537,22 +8649,22 @@
       </c>
       <c r="B157" s="38" t="inlineStr">
         <is>
-          <t>Selby Instruments</t>
+          <t>Caldwell Diagnostics</t>
         </is>
       </c>
       <c r="C157" s="38" t="inlineStr">
         <is>
-          <t>Vikram Nair</t>
+          <t>Malia Moreau</t>
         </is>
       </c>
       <c r="D157" s="53" t="inlineStr">
         <is>
-          <t>vnair@selbyinst.com</t>
+          <t>m.moreau@caldwelldx.com</t>
         </is>
       </c>
       <c r="E157" s="38" t="inlineStr">
         <is>
-          <t>Inbound — Demo request</t>
+          <t>Existing client — expansion</t>
         </is>
       </c>
       <c r="F157" s="38" t="inlineStr">
@@ -8565,7 +8677,7 @@
       </c>
       <c r="H157" s="38" t="inlineStr">
         <is>
-          <t>Devon Blackthorne</t>
+          <t>Amara Okonkwo</t>
         </is>
       </c>
       <c r="I157" s="38" t="inlineStr">
@@ -8574,7 +8686,7 @@
         </is>
       </c>
       <c r="J157" s="55" t="n">
-        <v>50000</v>
+        <v>65000</v>
       </c>
     </row>
     <row r="158" ht="21" customHeight="1">
@@ -8590,12 +8702,12 @@
       </c>
       <c r="C158" s="41" t="inlineStr">
         <is>
-          <t>Aisha Khan</t>
+          <t>Bianca Nowak</t>
         </is>
       </c>
       <c r="D158" s="49" t="inlineStr">
         <is>
-          <t>akhan@thornburybio.com</t>
+          <t>b.nowak@thornburybio.com</t>
         </is>
       </c>
       <c r="E158" s="41" t="inlineStr">
@@ -8638,12 +8750,12 @@
       </c>
       <c r="C159" s="38" t="inlineStr">
         <is>
-          <t>Marcus Weiss</t>
+          <t>Umar Yilmaz</t>
         </is>
       </c>
       <c r="D159" s="53" t="inlineStr">
         <is>
-          <t>mweiss@argentmol.com</t>
+          <t>u.yilmaz@argentmol.com</t>
         </is>
       </c>
       <c r="E159" s="38" t="inlineStr">
@@ -8686,12 +8798,12 @@
       </c>
       <c r="C160" s="41" t="inlineStr">
         <is>
-          <t>Priyanka Iyer</t>
+          <t>Oscar Sharma</t>
         </is>
       </c>
       <c r="D160" s="49" t="inlineStr">
         <is>
-          <t>piyer@beaconassay.com</t>
+          <t>o.sharma@beaconassay.com</t>
         </is>
       </c>
       <c r="E160" s="41" t="inlineStr">
@@ -8734,12 +8846,12 @@
       </c>
       <c r="C161" s="38" t="inlineStr">
         <is>
-          <t>Boris Sokolov</t>
+          <t>Kenji Ferreira</t>
         </is>
       </c>
       <c r="D161" s="53" t="inlineStr">
         <is>
-          <t>bsokolov@coveinst.com</t>
+          <t>k.ferreira@coveinst.com</t>
         </is>
       </c>
       <c r="E161" s="38" t="inlineStr">
@@ -8782,12 +8894,12 @@
       </c>
       <c r="C162" s="41" t="inlineStr">
         <is>
-          <t>Petra Volkov</t>
+          <t>Jamal Kapoor</t>
         </is>
       </c>
       <c r="D162" s="49" t="inlineStr">
         <is>
-          <t>pvolkov@delaneybio.com</t>
+          <t>j.kapoor@delaneybio.com</t>
         </is>
       </c>
       <c r="E162" s="41" t="inlineStr">
@@ -8830,12 +8942,12 @@
       </c>
       <c r="C163" s="38" t="inlineStr">
         <is>
-          <t>Neha Kapoor</t>
+          <t>Henry Moreau</t>
         </is>
       </c>
       <c r="D163" s="53" t="inlineStr">
         <is>
-          <t>nkapoor@enfieldreagents.com</t>
+          <t>h.moreau@enfieldreagents.com</t>
         </is>
       </c>
       <c r="E163" s="38" t="inlineStr">
@@ -8878,12 +8990,12 @@
       </c>
       <c r="C164" s="41" t="inlineStr">
         <is>
-          <t>Owen Booker</t>
+          <t>Cormac Sato</t>
         </is>
       </c>
       <c r="D164" s="49" t="inlineStr">
         <is>
-          <t>obooker@fenlanddx.com</t>
+          <t>c.sato@fenlanddx.com</t>
         </is>
       </c>
       <c r="E164" s="41" t="inlineStr">
@@ -8926,12 +9038,12 @@
       </c>
       <c r="C165" s="38" t="inlineStr">
         <is>
-          <t>Kai Nakamura</t>
+          <t>Neha Farouk</t>
         </is>
       </c>
       <c r="D165" s="53" t="inlineStr">
         <is>
-          <t>knakamura@corvexmol.com</t>
+          <t>n.farouk@corvexmol.com</t>
         </is>
       </c>
       <c r="E165" s="38" t="inlineStr">
@@ -8974,12 +9086,12 @@
       </c>
       <c r="C166" s="41" t="inlineStr">
         <is>
-          <t>Deepak Ramaswamy</t>
+          <t>Alistair Osei</t>
         </is>
       </c>
       <c r="D166" s="49" t="inlineStr">
         <is>
-          <t>dramaswamy@radialbio.com</t>
+          <t>a.osei@radialbio.com</t>
         </is>
       </c>
       <c r="E166" s="41" t="inlineStr">
@@ -9022,12 +9134,12 @@
       </c>
       <c r="C167" s="38" t="inlineStr">
         <is>
-          <t>Diya Chandra</t>
+          <t>Selin Solheim</t>
         </is>
       </c>
       <c r="D167" s="53" t="inlineStr">
         <is>
-          <t>dchandra@larkspurbio.com</t>
+          <t>s.solheim@larkspurbio.com</t>
         </is>
       </c>
       <c r="E167" s="38" t="inlineStr">
@@ -9070,12 +9182,12 @@
       </c>
       <c r="C168" s="41" t="inlineStr">
         <is>
-          <t>Klaus Baumann</t>
+          <t>Hana Janik</t>
         </is>
       </c>
       <c r="D168" s="49" t="inlineStr">
         <is>
-          <t>kbaumann@ashcroftassays.com</t>
+          <t>h.janik@ashcroftassays.com</t>
         </is>
       </c>
       <c r="E168" s="41" t="inlineStr">
@@ -9118,12 +9230,12 @@
       </c>
       <c r="C169" s="38" t="inlineStr">
         <is>
-          <t>Amir Hassan</t>
+          <t>Ivaan Winterbourne</t>
         </is>
       </c>
       <c r="D169" s="53" t="inlineStr">
         <is>
-          <t>ahassan@bellwetherreagents.com</t>
+          <t>i.winterbourne@bellwetherreagents.com</t>
         </is>
       </c>
       <c r="E169" s="38" t="inlineStr">
@@ -9166,12 +9278,12 @@
       </c>
       <c r="C170" s="41" t="inlineStr">
         <is>
-          <t>Sanjay Krishnamurthy</t>
+          <t>Imani Ferreira</t>
         </is>
       </c>
       <c r="D170" s="49" t="inlineStr">
         <is>
-          <t>s.krishnamurthy@halcyonanalytical.com</t>
+          <t>i.ferreira@halcyonanalytical.com</t>
         </is>
       </c>
       <c r="E170" s="41" t="inlineStr">
@@ -9214,12 +9326,12 @@
       </c>
       <c r="C171" s="38" t="inlineStr">
         <is>
-          <t>Ana Silva</t>
+          <t>Tariq Beaulieu</t>
         </is>
       </c>
       <c r="D171" s="53" t="inlineStr">
         <is>
-          <t>asilva@meadowbrookgx.com</t>
+          <t>t.beaulieu@meadowbrookgx.com</t>
         </is>
       </c>
       <c r="E171" s="38" t="inlineStr">
@@ -9262,12 +9374,12 @@
       </c>
       <c r="C172" s="41" t="inlineStr">
         <is>
-          <t>Malia Kekoa</t>
+          <t>Sofia Sokolov</t>
         </is>
       </c>
       <c r="D172" s="49" t="inlineStr">
         <is>
-          <t>mkekoa@silverpinetx.com</t>
+          <t>s.sokolov@silverpinetx.com</t>
         </is>
       </c>
       <c r="E172" s="41" t="inlineStr">
@@ -9310,12 +9422,12 @@
       </c>
       <c r="C173" s="38" t="inlineStr">
         <is>
-          <t>Rachel Cortez</t>
+          <t>Imani Ostrowski</t>
         </is>
       </c>
       <c r="D173" s="53" t="inlineStr">
         <is>
-          <t>rcortez@windrowsci.com</t>
+          <t>i.ostrowski@windrowsci.com</t>
         </is>
       </c>
       <c r="E173" s="38" t="inlineStr">
@@ -9358,12 +9470,12 @@
       </c>
       <c r="C174" s="41" t="inlineStr">
         <is>
-          <t>Elena Cortez</t>
+          <t>Sofia Tanaka</t>
         </is>
       </c>
       <c r="D174" s="49" t="inlineStr">
         <is>
-          <t>ecortez@norwichbio.com</t>
+          <t>s.tanaka@norwichbio.com</t>
         </is>
       </c>
       <c r="E174" s="41" t="inlineStr">
@@ -9406,12 +9518,12 @@
       </c>
       <c r="C175" s="38" t="inlineStr">
         <is>
-          <t>Ananya Iyer</t>
+          <t>Aisha Larsen</t>
         </is>
       </c>
       <c r="D175" s="53" t="inlineStr">
         <is>
-          <t>aiyer@kestreldx.com</t>
+          <t>a.larsen@kestreldx.com</t>
         </is>
       </c>
       <c r="E175" s="38" t="inlineStr">
@@ -9454,12 +9566,12 @@
       </c>
       <c r="C176" s="41" t="inlineStr">
         <is>
-          <t>Nathan Osei</t>
+          <t>Leila Ainsley</t>
         </is>
       </c>
       <c r="D176" s="49" t="inlineStr">
         <is>
-          <t>nathan.osei@northgatebiolabs.com</t>
+          <t>l.ainsley@northgatebiolabs.com</t>
         </is>
       </c>
       <c r="E176" s="41" t="inlineStr">
@@ -9502,12 +9614,12 @@
       </c>
       <c r="C177" s="38" t="inlineStr">
         <is>
-          <t>Aarav Bhatt</t>
+          <t>Ingrid Verma</t>
         </is>
       </c>
       <c r="D177" s="53" t="inlineStr">
         <is>
-          <t>abhatt@sedgwickreagents.com</t>
+          <t>i.verma@sedgwickreagents.com</t>
         </is>
       </c>
       <c r="E177" s="38" t="inlineStr">
@@ -9550,12 +9662,12 @@
       </c>
       <c r="C178" s="41" t="inlineStr">
         <is>
-          <t>Naveen Chandra</t>
+          <t>Renata Osei</t>
         </is>
       </c>
       <c r="D178" s="49" t="inlineStr">
         <is>
-          <t>nchandra@ashvalemol.com</t>
+          <t>r.osei@ashvalemol.com</t>
         </is>
       </c>
       <c r="E178" s="41" t="inlineStr">
@@ -9598,12 +9710,12 @@
       </c>
       <c r="C179" s="38" t="inlineStr">
         <is>
-          <t>Priya Menon</t>
+          <t>Priyanka Quintero</t>
         </is>
       </c>
       <c r="D179" s="53" t="inlineStr">
         <is>
-          <t>pmenon@chartwellinst.com</t>
+          <t>p.quintero@chartwellinst.com</t>
         </is>
       </c>
       <c r="E179" s="38" t="inlineStr">
@@ -9646,12 +9758,12 @@
       </c>
       <c r="C180" s="41" t="inlineStr">
         <is>
-          <t>Fatima Farouk</t>
+          <t>Rohit Wei</t>
         </is>
       </c>
       <c r="D180" s="49" t="inlineStr">
         <is>
-          <t>ffarouk@draycottgx.com</t>
+          <t>r.wei@draycottgx.com</t>
         </is>
       </c>
       <c r="E180" s="41" t="inlineStr">
@@ -9694,12 +9806,12 @@
       </c>
       <c r="C181" s="38" t="inlineStr">
         <is>
-          <t>Ivaan Sharma</t>
+          <t>Magnus Manaia</t>
         </is>
       </c>
       <c r="D181" s="53" t="inlineStr">
         <is>
-          <t>isharma@elmwoodbio.com</t>
+          <t>m.manaia@elmwoodbio.com</t>
         </is>
       </c>
       <c r="E181" s="38" t="inlineStr">
@@ -9742,12 +9854,12 @@
       </c>
       <c r="C182" s="41" t="inlineStr">
         <is>
-          <t>Anaya Patel</t>
+          <t>Freya Nazarov</t>
         </is>
       </c>
       <c r="D182" s="49" t="inlineStr">
         <is>
-          <t>apatel@ferncliffdx.com</t>
+          <t>f.nazarov@ferncliffdx.com</t>
         </is>
       </c>
       <c r="E182" s="41" t="inlineStr">
@@ -9790,12 +9902,12 @@
       </c>
       <c r="C183" s="38" t="inlineStr">
         <is>
-          <t>Boris Sokolov</t>
+          <t>Viktor Beringer</t>
         </is>
       </c>
       <c r="D183" s="53" t="inlineStr">
         <is>
-          <t>b.sokolov@gairlochanalytical.com</t>
+          <t>v.beringer@gairlochanalytical.com</t>
         </is>
       </c>
       <c r="E183" s="38" t="inlineStr">
@@ -9838,12 +9950,12 @@
       </c>
       <c r="C184" s="41" t="inlineStr">
         <is>
-          <t>Jamal Booker</t>
+          <t>Klaus Lindqvist</t>
         </is>
       </c>
       <c r="D184" s="49" t="inlineStr">
         <is>
-          <t>j.booker@harborlightbio.com</t>
+          <t>k.lindqvist@harborlightbio.com</t>
         </is>
       </c>
       <c r="E184" s="41" t="inlineStr">
@@ -9886,12 +9998,12 @@
       </c>
       <c r="C185" s="38" t="inlineStr">
         <is>
-          <t>Zara Ahmed</t>
+          <t>Gustav Zajac</t>
         </is>
       </c>
       <c r="D185" s="53" t="inlineStr">
         <is>
-          <t>zahmed@isleyreagents.com</t>
+          <t>g.zajac@isleyreagents.com</t>
         </is>
       </c>
       <c r="E185" s="38" t="inlineStr">
@@ -9934,12 +10046,12 @@
       </c>
       <c r="C186" s="41" t="inlineStr">
         <is>
-          <t>Nikolai Petrov</t>
+          <t>Freya Kekoa</t>
         </is>
       </c>
       <c r="D186" s="49" t="inlineStr">
         <is>
-          <t>npetrov@jerbrookdx.com</t>
+          <t>f.kekoa@jerbrookdx.com</t>
         </is>
       </c>
       <c r="E186" s="41" t="inlineStr">
@@ -9982,12 +10094,12 @@
       </c>
       <c r="C187" s="38" t="inlineStr">
         <is>
-          <t>Devon Cabrera</t>
+          <t>Umar Chandra</t>
         </is>
       </c>
       <c r="D187" s="53" t="inlineStr">
         <is>
-          <t>dcabrera@kilburnmol.com</t>
+          <t>u.chandra@kilburnmol.com</t>
         </is>
       </c>
       <c r="E187" s="38" t="inlineStr">
@@ -10030,12 +10142,12 @@
       </c>
       <c r="C188" s="41" t="inlineStr">
         <is>
-          <t>Elena Baumann</t>
+          <t>Marcus Cortez</t>
         </is>
       </c>
       <c r="D188" s="49" t="inlineStr">
         <is>
-          <t>e.baumann@ledburyassays.com</t>
+          <t>m.cortez@ledburyassays.com</t>
         </is>
       </c>
       <c r="E188" s="41" t="inlineStr">
@@ -10078,12 +10190,12 @@
       </c>
       <c r="C189" s="38" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Malia Lombardi</t>
         </is>
       </c>
       <c r="D189" s="53" t="inlineStr">
         <is>
-          <t>sofia.marchetti@meritbio.com</t>
+          <t>m.lombardi@meritbio.com</t>
         </is>
       </c>
       <c r="E189" s="38" t="inlineStr">
@@ -10126,12 +10238,12 @@
       </c>
       <c r="C190" s="41" t="inlineStr">
         <is>
-          <t>Rangi Osei</t>
+          <t>Cormac Terzic</t>
         </is>
       </c>
       <c r="D190" s="49" t="inlineStr">
         <is>
-          <t>rangi.osei@newburyinst.com</t>
+          <t>c.terzic@newburyinst.com</t>
         </is>
       </c>
       <c r="E190" s="41" t="inlineStr">
@@ -10174,12 +10286,12 @@
       </c>
       <c r="C191" s="38" t="inlineStr">
         <is>
-          <t>Aisha Khan</t>
+          <t>Grace Lombardi</t>
         </is>
       </c>
       <c r="D191" s="53" t="inlineStr">
         <is>
-          <t>a.khan@orleansgx.com</t>
+          <t>g.lombardi@orleansgx.com</t>
         </is>
       </c>
       <c r="E191" s="38" t="inlineStr">
@@ -10222,12 +10334,12 @@
       </c>
       <c r="C192" s="41" t="inlineStr">
         <is>
-          <t>Richard Ainsley</t>
+          <t>Amelia Nakamura</t>
         </is>
       </c>
       <c r="D192" s="49" t="inlineStr">
         <is>
-          <t>r.ainsley2@pembertondx.com</t>
+          <t>a.nakamura@pembertondx.com</t>
         </is>
       </c>
       <c r="E192" s="41" t="inlineStr">
@@ -10270,12 +10382,12 @@
       </c>
       <c r="C193" s="38" t="inlineStr">
         <is>
-          <t>Ingrid Larsen</t>
+          <t>Nadia Quintero</t>
         </is>
       </c>
       <c r="D193" s="53" t="inlineStr">
         <is>
-          <t>i.larsen@quentonbiolabs.com</t>
+          <t>n.quintero@quentonbiolabs.com</t>
         </is>
       </c>
       <c r="E193" s="38" t="inlineStr">
@@ -10318,12 +10430,12 @@
       </c>
       <c r="C194" s="41" t="inlineStr">
         <is>
-          <t>Vikram Nair</t>
+          <t>Tariq Vasquez</t>
         </is>
       </c>
       <c r="D194" s="49" t="inlineStr">
         <is>
-          <t>v.nair@ramseyanalytical.com</t>
+          <t>t.vasquez@ramseyanalytical.com</t>
         </is>
       </c>
       <c r="E194" s="41" t="inlineStr">
@@ -10366,12 +10478,12 @@
       </c>
       <c r="C195" s="38" t="inlineStr">
         <is>
-          <t>Anika Menon</t>
+          <t>Nia Chiu</t>
         </is>
       </c>
       <c r="D195" s="53" t="inlineStr">
         <is>
-          <t>a.menon@sutherlandreagents.com</t>
+          <t>n.chiu@sutherlandreagents.com</t>
         </is>
       </c>
       <c r="E195" s="38" t="inlineStr">
@@ -10414,12 +10526,12 @@
       </c>
       <c r="C196" s="41" t="inlineStr">
         <is>
-          <t>Klaus Baumann</t>
+          <t>Amir Petrov</t>
         </is>
       </c>
       <c r="D196" s="49" t="inlineStr">
         <is>
-          <t>k.baumann@trellismol.com</t>
+          <t>a.petrov@trellismol.com</t>
         </is>
       </c>
       <c r="E196" s="41" t="inlineStr">
@@ -10462,12 +10574,12 @@
       </c>
       <c r="C197" s="38" t="inlineStr">
         <is>
-          <t>Yuki Sato</t>
+          <t>Chen Ustinov</t>
         </is>
       </c>
       <c r="D197" s="53" t="inlineStr">
         <is>
-          <t>y.sato@underhillbio.com</t>
+          <t>c.ustinov@underhillbio.com</t>
         </is>
       </c>
       <c r="E197" s="38" t="inlineStr">
@@ -10510,12 +10622,12 @@
       </c>
       <c r="C198" s="41" t="inlineStr">
         <is>
-          <t>Ishaan Verma</t>
+          <t>Oscar Kapoor</t>
         </is>
       </c>
       <c r="D198" s="49" t="inlineStr">
         <is>
-          <t>i.verma@veronaassays.com</t>
+          <t>o.kapoor@veronaassays.com</t>
         </is>
       </c>
       <c r="E198" s="41" t="inlineStr">
@@ -10558,12 +10670,12 @@
       </c>
       <c r="C199" s="38" t="inlineStr">
         <is>
-          <t>Neha Kapoor</t>
+          <t>Jovana Kapoor</t>
         </is>
       </c>
       <c r="D199" s="53" t="inlineStr">
         <is>
-          <t>n.kapoor@whitfielddx.com</t>
+          <t>j.kapoor@whitfielddx.com</t>
         </is>
       </c>
       <c r="E199" s="38" t="inlineStr">
@@ -10606,12 +10718,12 @@
       </c>
       <c r="C200" s="41" t="inlineStr">
         <is>
-          <t>Amir Hassan</t>
+          <t>Hana Haddad</t>
         </is>
       </c>
       <c r="D200" s="49" t="inlineStr">
         <is>
-          <t>a.hassan@xantheinst.com</t>
+          <t>h.haddad@xantheinst.com</t>
         </is>
       </c>
       <c r="E200" s="41" t="inlineStr">
@@ -10654,12 +10766,12 @@
       </c>
       <c r="C201" s="38" t="inlineStr">
         <is>
-          <t>Marcus Weiss</t>
+          <t>Zara Nowak</t>
         </is>
       </c>
       <c r="D201" s="53" t="inlineStr">
         <is>
-          <t>m.weiss@yorktownbio.com</t>
+          <t>z.nowak@yorktownbio.com</t>
         </is>
       </c>
       <c r="E201" s="38" t="inlineStr">
@@ -10702,12 +10814,12 @@
       </c>
       <c r="C202" s="41" t="inlineStr">
         <is>
-          <t>Sanjay Krishnamurthy</t>
+          <t>Priya Al-Sayed</t>
         </is>
       </c>
       <c r="D202" s="49" t="inlineStr">
         <is>
-          <t>sanjay.k@zephyrgx.com</t>
+          <t>p.al-sayed@zephyrgx.com</t>
         </is>
       </c>
       <c r="E202" s="41" t="inlineStr">
@@ -10750,12 +10862,12 @@
       </c>
       <c r="C203" s="38" t="inlineStr">
         <is>
-          <t>Malia Kekoa</t>
+          <t>Yasmin Grondin</t>
         </is>
       </c>
       <c r="D203" s="53" t="inlineStr">
         <is>
-          <t>m.kekoa@aldermandx.com</t>
+          <t>y.grondin@aldermandx.com</t>
         </is>
       </c>
       <c r="E203" s="38" t="inlineStr">
@@ -10798,12 +10910,12 @@
       </c>
       <c r="C204" s="41" t="inlineStr">
         <is>
-          <t>Deepak Ramaswamy</t>
+          <t>Mikhail Yilmaz</t>
         </is>
       </c>
       <c r="D204" s="49" t="inlineStr">
         <is>
-          <t>d.ramaswamy@bosworthbio.com</t>
+          <t>m.yilmaz@bosworthbio.com</t>
         </is>
       </c>
       <c r="E204" s="41" t="inlineStr">
@@ -10846,12 +10958,12 @@
       </c>
       <c r="C205" s="38" t="inlineStr">
         <is>
-          <t>Ana Silva</t>
+          <t>Amir Mancini</t>
         </is>
       </c>
       <c r="D205" s="53" t="inlineStr">
         <is>
-          <t>a.silva@colvinreagents.com</t>
+          <t>a.mancini@colvinreagents.com</t>
         </is>
       </c>
       <c r="E205" s="38" t="inlineStr">
@@ -10894,12 +11006,12 @@
       </c>
       <c r="C206" s="41" t="inlineStr">
         <is>
-          <t>Kai Nakamura</t>
+          <t>Vera Falcon</t>
         </is>
       </c>
       <c r="D206" s="49" t="inlineStr">
         <is>
-          <t>k.nakamura@deerfieldmol.com</t>
+          <t>v.falcon@deerfieldmol.com</t>
         </is>
       </c>
       <c r="E206" s="41" t="inlineStr">
@@ -10942,12 +11054,12 @@
       </c>
       <c r="C207" s="38" t="inlineStr">
         <is>
-          <t>Petra Volkov</t>
+          <t>Oscar Farouk</t>
         </is>
       </c>
       <c r="D207" s="53" t="inlineStr">
         <is>
-          <t>p.volkov@estwickinst.com</t>
+          <t>o.farouk@estwickinst.com</t>
         </is>
       </c>
       <c r="E207" s="38" t="inlineStr">
@@ -10990,12 +11102,12 @@
       </c>
       <c r="C208" s="41" t="inlineStr">
         <is>
-          <t>Chen Wei</t>
+          <t>Boris Grondin</t>
         </is>
       </c>
       <c r="D208" s="49" t="inlineStr">
         <is>
-          <t>c.wei@fairhavenanalytical.com</t>
+          <t>b.grondin@fairhavenanalytical.com</t>
         </is>
       </c>
       <c r="E208" s="41" t="inlineStr">
@@ -11038,12 +11150,12 @@
       </c>
       <c r="C209" s="38" t="inlineStr">
         <is>
-          <t>Fatima Farouk</t>
+          <t>Torsten Orozco</t>
         </is>
       </c>
       <c r="D209" s="53" t="inlineStr">
         <is>
-          <t>f.farouk@glenridgebiolabs.com</t>
+          <t>t.orozco@glenridgebiolabs.com</t>
         </is>
       </c>
       <c r="E209" s="38" t="inlineStr">
@@ -11086,12 +11198,12 @@
       </c>
       <c r="C210" s="41" t="inlineStr">
         <is>
-          <t>Nathan Osei</t>
+          <t>Kenji Okafor</t>
         </is>
       </c>
       <c r="D210" s="49" t="inlineStr">
         <is>
-          <t>nathan.osei@halewooddx.com</t>
+          <t>k.okafor@halewooddx.com</t>
         </is>
       </c>
       <c r="E210" s="41" t="inlineStr">
@@ -11134,12 +11246,12 @@
       </c>
       <c r="C211" s="38" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Jamal Wei</t>
         </is>
       </c>
       <c r="D211" s="53" t="inlineStr">
         <is>
-          <t>r.sharma@ivywoodassays.com</t>
+          <t>j.wei@ivywoodassays.com</t>
         </is>
       </c>
       <c r="E211" s="38" t="inlineStr">
@@ -11169,54 +11281,7 @@
         <v>36500</v>
       </c>
     </row>
-    <row r="212" ht="21" customHeight="1">
-      <c r="A212" s="48" t="inlineStr">
-        <is>
-          <t>L-25Q4-0211</t>
-        </is>
-      </c>
-      <c r="B212" s="41" t="inlineStr">
-        <is>
-          <t>Caldwell Diagnostics</t>
-        </is>
-      </c>
-      <c r="C212" s="41" t="inlineStr">
-        <is>
-          <t>Robert Ainsley</t>
-        </is>
-      </c>
-      <c r="D212" s="49" t="inlineStr">
-        <is>
-          <t>rainsley@caldwelldx.com</t>
-        </is>
-      </c>
-      <c r="E212" s="41" t="inlineStr">
-        <is>
-          <t>Existing client — expansion</t>
-        </is>
-      </c>
-      <c r="F212" s="41" t="inlineStr">
-        <is>
-          <t>Sales-Touched</t>
-        </is>
-      </c>
-      <c r="G212" s="50" t="n">
-        <v>45999</v>
-      </c>
-      <c r="H212" s="41" t="inlineStr">
-        <is>
-          <t>Amara Okonkwo</t>
-        </is>
-      </c>
-      <c r="I212" s="41" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="J212" s="51" t="n">
-        <v>65000</v>
-      </c>
-    </row>
+    <row r="212" ht="21" customHeight="1"/>
   </sheetData>
   <autoFilter ref="A1:J211"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11243,7 +11308,6 @@
           <t>Extract Metadata</t>
         </is>
       </c>
-      <c r="B1" s="30" t="n"/>
     </row>
     <row r="2" ht="14" customHeight="1"/>
     <row r="3" ht="38" customHeight="1">

--- a/filesystem/MarketingOps/CRM/Q4_2025_crm_export.xlsx
+++ b/filesystem/MarketingOps/CRM/Q4_2025_crm_export.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Footer" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Footer" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$J$211</definedName>
@@ -27,7 +27,7 @@
     <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="168" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -112,6 +112,11 @@
     <font>
       <name val="Segoe UI"/>
       <color rgb="000284C7"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="FF1E40AF"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -387,7 +392,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -568,6 +573,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1217,7 +1228,7 @@
           <t>Pia Nazarov</t>
         </is>
       </c>
-      <c r="D2" s="49" t="inlineStr">
+      <c r="D2" s="68" t="inlineStr">
         <is>
           <t>p.nazarov@fenlanddx.com</t>
         </is>
@@ -1265,7 +1276,7 @@
           <t>Simone Petrov</t>
         </is>
       </c>
-      <c r="D3" s="53" t="inlineStr">
+      <c r="D3" s="69" t="inlineStr">
         <is>
           <t>s.petrov@corvexmol.com</t>
         </is>
@@ -1313,7 +1324,7 @@
           <t>Stellan Vasquez</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="68" t="inlineStr">
         <is>
           <t>s.vasquez@radialbio.com</t>
         </is>
@@ -1361,7 +1372,7 @@
           <t>Felix Castellanos</t>
         </is>
       </c>
-      <c r="D5" s="53" t="inlineStr">
+      <c r="D5" s="69" t="inlineStr">
         <is>
           <t>f.castellanos@larkspurbio.com</t>
         </is>
@@ -1409,7 +1420,7 @@
           <t>Ivaan Isaev</t>
         </is>
       </c>
-      <c r="D6" s="49" t="inlineStr">
+      <c r="D6" s="68" t="inlineStr">
         <is>
           <t>i.isaev@ashcroftassays.com</t>
         </is>
@@ -1457,7 +1468,7 @@
           <t>Sanjay Manaia</t>
         </is>
       </c>
-      <c r="D7" s="53" t="inlineStr">
+      <c r="D7" s="69" t="inlineStr">
         <is>
           <t>s.manaia@bellwetherreagents.com</t>
         </is>
@@ -1505,7 +1516,7 @@
           <t>Talia Kallas</t>
         </is>
       </c>
-      <c r="D8" s="49" t="inlineStr">
+      <c r="D8" s="68" t="inlineStr">
         <is>
           <t>t.kallas@halcyonanalytical.com</t>
         </is>
@@ -1553,7 +1564,7 @@
           <t>Aroha Radu</t>
         </is>
       </c>
-      <c r="D9" s="53" t="inlineStr">
+      <c r="D9" s="69" t="inlineStr">
         <is>
           <t>a.radu@meadowbrookgx.com</t>
         </is>
@@ -1601,7 +1612,7 @@
           <t>Nathan Mancini</t>
         </is>
       </c>
-      <c r="D10" s="49" t="inlineStr">
+      <c r="D10" s="68" t="inlineStr">
         <is>
           <t>n.mancini@silverpinetx.com</t>
         </is>
@@ -1649,7 +1660,7 @@
           <t>Ravi Janik</t>
         </is>
       </c>
-      <c r="D11" s="53" t="inlineStr">
+      <c r="D11" s="69" t="inlineStr">
         <is>
           <t>r.janik@windrowsci.com</t>
         </is>
@@ -1697,7 +1708,7 @@
           <t>Paloma Okafor</t>
         </is>
       </c>
-      <c r="D12" s="49" t="inlineStr">
+      <c r="D12" s="68" t="inlineStr">
         <is>
           <t>p.okafor@norwichbio.com</t>
         </is>
@@ -1745,7 +1756,7 @@
           <t>Gustav Dahl</t>
         </is>
       </c>
-      <c r="D13" s="53" t="inlineStr">
+      <c r="D13" s="69" t="inlineStr">
         <is>
           <t>g.dahl@kestreldx.com</t>
         </is>
@@ -1793,7 +1804,7 @@
           <t>Pia Beringer</t>
         </is>
       </c>
-      <c r="D14" s="49" t="inlineStr">
+      <c r="D14" s="68" t="inlineStr">
         <is>
           <t>p.beringer@northgatebiolabs.com</t>
         </is>
@@ -1841,7 +1852,7 @@
           <t>Priyanka Zimmerman</t>
         </is>
       </c>
-      <c r="D15" s="53" t="inlineStr">
+      <c r="D15" s="69" t="inlineStr">
         <is>
           <t>p.zimmerman@sedgwickreagents.com</t>
         </is>
@@ -1889,7 +1900,7 @@
           <t>Malia Orozco</t>
         </is>
       </c>
-      <c r="D16" s="49" t="inlineStr">
+      <c r="D16" s="68" t="inlineStr">
         <is>
           <t>m.orozco@ashvalemol.com</t>
         </is>
@@ -1937,7 +1948,7 @@
           <t>Kenji Moreau</t>
         </is>
       </c>
-      <c r="D17" s="53" t="inlineStr">
+      <c r="D17" s="69" t="inlineStr">
         <is>
           <t>k.moreau@chartwellinst.com</t>
         </is>
@@ -1985,7 +1996,7 @@
           <t>Tariq Onyekachi</t>
         </is>
       </c>
-      <c r="D18" s="49" t="inlineStr">
+      <c r="D18" s="68" t="inlineStr">
         <is>
           <t>t.onyekachi@draycottgx.com</t>
         </is>
@@ -2033,7 +2044,7 @@
           <t>Deepak Beaulieu</t>
         </is>
       </c>
-      <c r="D19" s="53" t="inlineStr">
+      <c r="D19" s="69" t="inlineStr">
         <is>
           <t>d.beaulieu@elmwoodbio.com</t>
         </is>
@@ -2081,7 +2092,7 @@
           <t>Stellan Ulrich</t>
         </is>
       </c>
-      <c r="D20" s="49" t="inlineStr">
+      <c r="D20" s="68" t="inlineStr">
         <is>
           <t>s.ulrich@ferncliffdx.com</t>
         </is>
@@ -2129,7 +2140,7 @@
           <t>Petra Cabrera</t>
         </is>
       </c>
-      <c r="D21" s="53" t="inlineStr">
+      <c r="D21" s="69" t="inlineStr">
         <is>
           <t>p.cabrera@gairlochanalytical.com</t>
         </is>
@@ -2177,7 +2188,7 @@
           <t>Boris Baumann</t>
         </is>
       </c>
-      <c r="D22" s="49" t="inlineStr">
+      <c r="D22" s="68" t="inlineStr">
         <is>
           <t>b.baumann@harborlightbio.com</t>
         </is>
@@ -2225,7 +2236,7 @@
           <t>Umar Delgado</t>
         </is>
       </c>
-      <c r="D23" s="53" t="inlineStr">
+      <c r="D23" s="69" t="inlineStr">
         <is>
           <t>u.delgado@isleyreagents.com</t>
         </is>
@@ -2273,7 +2284,7 @@
           <t>Kofi Farouk</t>
         </is>
       </c>
-      <c r="D24" s="49" t="inlineStr">
+      <c r="D24" s="68" t="inlineStr">
         <is>
           <t>k.farouk@jerbrookdx.com</t>
         </is>
@@ -2321,7 +2332,7 @@
           <t>Owen Nazarov</t>
         </is>
       </c>
-      <c r="D25" s="53" t="inlineStr">
+      <c r="D25" s="69" t="inlineStr">
         <is>
           <t>o.nazarov@kilburnmol.com</t>
         </is>
@@ -2369,7 +2380,7 @@
           <t>Devon Mancini</t>
         </is>
       </c>
-      <c r="D26" s="49" t="inlineStr">
+      <c r="D26" s="68" t="inlineStr">
         <is>
           <t>d.mancini@ledburyassays.com</t>
         </is>
@@ -2417,7 +2428,7 @@
           <t>Devon Eriksson</t>
         </is>
       </c>
-      <c r="D27" s="53" t="inlineStr">
+      <c r="D27" s="69" t="inlineStr">
         <is>
           <t>d.eriksson@meritbio.com</t>
         </is>
@@ -2465,7 +2476,7 @@
           <t>Wei Al-Sayed</t>
         </is>
       </c>
-      <c r="D28" s="49" t="inlineStr">
+      <c r="D28" s="68" t="inlineStr">
         <is>
           <t>w.al-sayed@newburyinst.com</t>
         </is>
@@ -2513,7 +2524,7 @@
           <t>Kenji Sokolova</t>
         </is>
       </c>
-      <c r="D29" s="53" t="inlineStr">
+      <c r="D29" s="69" t="inlineStr">
         <is>
           <t>k.sokolova@orleansgx.com</t>
         </is>
@@ -2561,7 +2572,7 @@
           <t>Sofia Vasquez</t>
         </is>
       </c>
-      <c r="D30" s="49" t="inlineStr">
+      <c r="D30" s="68" t="inlineStr">
         <is>
           <t>s.vasquez@pembertondx.com</t>
         </is>
@@ -2609,7 +2620,7 @@
           <t>Malia Rivas</t>
         </is>
       </c>
-      <c r="D31" s="53" t="inlineStr">
+      <c r="D31" s="69" t="inlineStr">
         <is>
           <t>m.rivas@quentonbiolabs.com</t>
         </is>
@@ -2657,7 +2668,7 @@
           <t>Edvard Ferreira</t>
         </is>
       </c>
-      <c r="D32" s="49" t="inlineStr">
+      <c r="D32" s="68" t="inlineStr">
         <is>
           <t>e.ferreira@ramseyanalytical.com</t>
         </is>
@@ -2705,7 +2716,7 @@
           <t>Wren Kekoa</t>
         </is>
       </c>
-      <c r="D33" s="53" t="inlineStr">
+      <c r="D33" s="69" t="inlineStr">
         <is>
           <t>w.kekoa@sutherlandreagents.com</t>
         </is>
@@ -2753,7 +2764,7 @@
           <t>Esther Kapoor</t>
         </is>
       </c>
-      <c r="D34" s="49" t="inlineStr">
+      <c r="D34" s="68" t="inlineStr">
         <is>
           <t>e.kapoor@trellismol.com</t>
         </is>
@@ -2801,7 +2812,7 @@
           <t>Nia Papadopoulos</t>
         </is>
       </c>
-      <c r="D35" s="53" t="inlineStr">
+      <c r="D35" s="69" t="inlineStr">
         <is>
           <t>n.papadopoulos@underhillbio.com</t>
         </is>
@@ -2849,7 +2860,7 @@
           <t>Aisha Novak</t>
         </is>
       </c>
-      <c r="D36" s="49" t="inlineStr">
+      <c r="D36" s="68" t="inlineStr">
         <is>
           <t>a.novak@veronaassays.com</t>
         </is>
@@ -2897,7 +2908,7 @@
           <t>Kenji Rivas</t>
         </is>
       </c>
-      <c r="D37" s="53" t="inlineStr">
+      <c r="D37" s="69" t="inlineStr">
         <is>
           <t>k.rivas@whitfielddx.com</t>
         </is>
@@ -2945,7 +2956,7 @@
           <t>Larisa Novak</t>
         </is>
       </c>
-      <c r="D38" s="49" t="inlineStr">
+      <c r="D38" s="68" t="inlineStr">
         <is>
           <t>l.novak@xantheinst.com</t>
         </is>
@@ -2993,7 +3004,7 @@
           <t>Aroha Wei</t>
         </is>
       </c>
-      <c r="D39" s="53" t="inlineStr">
+      <c r="D39" s="69" t="inlineStr">
         <is>
           <t>a.wei@yorktownbio.com</t>
         </is>
@@ -3041,7 +3052,7 @@
           <t>Idris Petrescu</t>
         </is>
       </c>
-      <c r="D40" s="49" t="inlineStr">
+      <c r="D40" s="68" t="inlineStr">
         <is>
           <t>i.petrescu@zephyrgx.com</t>
         </is>
@@ -3089,7 +3100,7 @@
           <t>Giulia Quintero</t>
         </is>
       </c>
-      <c r="D41" s="53" t="inlineStr">
+      <c r="D41" s="69" t="inlineStr">
         <is>
           <t>g.quintero@aldermandx.com</t>
         </is>
@@ -3137,7 +3148,7 @@
           <t>Priya Sato</t>
         </is>
       </c>
-      <c r="D42" s="49" t="inlineStr">
+      <c r="D42" s="68" t="inlineStr">
         <is>
           <t>p.sato@bosworthbio.com</t>
         </is>
@@ -3185,7 +3196,7 @@
           <t>Idris Hoffmann</t>
         </is>
       </c>
-      <c r="D43" s="53" t="inlineStr">
+      <c r="D43" s="69" t="inlineStr">
         <is>
           <t>i.hoffmann@colvinreagents.com</t>
         </is>
@@ -3233,7 +3244,7 @@
           <t>Mikhail Marchand</t>
         </is>
       </c>
-      <c r="D44" s="49" t="inlineStr">
+      <c r="D44" s="68" t="inlineStr">
         <is>
           <t>m.marchand@deerfieldmol.com</t>
         </is>
@@ -3281,7 +3292,7 @@
           <t>Idris Dahl</t>
         </is>
       </c>
-      <c r="D45" s="53" t="inlineStr">
+      <c r="D45" s="69" t="inlineStr">
         <is>
           <t>i.dahl@estwickinst.com</t>
         </is>
@@ -3329,7 +3340,7 @@
           <t>Bianca Baumann</t>
         </is>
       </c>
-      <c r="D46" s="49" t="inlineStr">
+      <c r="D46" s="68" t="inlineStr">
         <is>
           <t>b.baumann@fairhavenanalytical.com</t>
         </is>
@@ -3377,7 +3388,7 @@
           <t>Paloma Falcon</t>
         </is>
       </c>
-      <c r="D47" s="53" t="inlineStr">
+      <c r="D47" s="69" t="inlineStr">
         <is>
           <t>p.falcon@glenridgebiolabs.com</t>
         </is>
@@ -3425,7 +3436,7 @@
           <t>Edvard Petrov</t>
         </is>
       </c>
-      <c r="D48" s="49" t="inlineStr">
+      <c r="D48" s="68" t="inlineStr">
         <is>
           <t>e.petrov@halewooddx.com</t>
         </is>
@@ -3473,7 +3484,7 @@
           <t>Yara Hoffmann</t>
         </is>
       </c>
-      <c r="D49" s="53" t="inlineStr">
+      <c r="D49" s="69" t="inlineStr">
         <is>
           <t>y.hoffmann@ivywoodassays.com</t>
         </is>
@@ -3521,7 +3532,7 @@
           <t>Mikhail Nikolic</t>
         </is>
       </c>
-      <c r="D50" s="49" t="inlineStr">
+      <c r="D50" s="68" t="inlineStr">
         <is>
           <t>m.nikolic@junctionreagents.com</t>
         </is>
@@ -3569,7 +3580,7 @@
           <t>Owen Mancini</t>
         </is>
       </c>
-      <c r="D51" s="53" t="inlineStr">
+      <c r="D51" s="69" t="inlineStr">
         <is>
           <t>o.mancini@keswickgx.com</t>
         </is>
@@ -3617,7 +3628,7 @@
           <t>Torsten Yilmaz</t>
         </is>
       </c>
-      <c r="D52" s="49" t="inlineStr">
+      <c r="D52" s="68" t="inlineStr">
         <is>
           <t>t.yilmaz@lyndhurstinst.com</t>
         </is>
@@ -3665,7 +3676,7 @@
           <t>Petra Ustinov</t>
         </is>
       </c>
-      <c r="D53" s="53" t="inlineStr">
+      <c r="D53" s="69" t="inlineStr">
         <is>
           <t>p.ustinov@marstonbio.com</t>
         </is>
@@ -3713,7 +3724,7 @@
           <t>Mateus Ainsley</t>
         </is>
       </c>
-      <c r="D54" s="49" t="inlineStr">
+      <c r="D54" s="68" t="inlineStr">
         <is>
           <t>m.ainsley@oakenwooddx.com</t>
         </is>
@@ -3761,7 +3772,7 @@
           <t>Hana Moreau</t>
         </is>
       </c>
-      <c r="D55" s="53" t="inlineStr">
+      <c r="D55" s="69" t="inlineStr">
         <is>
           <t>h.moreau@pentworthmol.com</t>
         </is>
@@ -3809,7 +3820,7 @@
           <t>Ishaan Janik</t>
         </is>
       </c>
-      <c r="D56" s="49" t="inlineStr">
+      <c r="D56" s="68" t="inlineStr">
         <is>
           <t>i.janik@quaywaterbiolabs.com</t>
         </is>
@@ -3857,7 +3868,7 @@
           <t>Quentin Onyekachi</t>
         </is>
       </c>
-      <c r="D57" s="53" t="inlineStr">
+      <c r="D57" s="69" t="inlineStr">
         <is>
           <t>q.onyekachi@rowtonreagents.com</t>
         </is>
@@ -3905,7 +3916,7 @@
           <t>Ana Ulrich</t>
         </is>
       </c>
-      <c r="D58" s="49" t="inlineStr">
+      <c r="D58" s="68" t="inlineStr">
         <is>
           <t>a.ulrich@tavistockassays.com</t>
         </is>
@@ -3953,7 +3964,7 @@
           <t>Xander Baumann</t>
         </is>
       </c>
-      <c r="D59" s="53" t="inlineStr">
+      <c r="D59" s="69" t="inlineStr">
         <is>
           <t>x.baumann@uxbridgegx.com</t>
         </is>
@@ -4001,7 +4012,7 @@
           <t>Esther Ustinov</t>
         </is>
       </c>
-      <c r="D60" s="49" t="inlineStr">
+      <c r="D60" s="68" t="inlineStr">
         <is>
           <t>e.ustinov@valloninst.com</t>
         </is>
@@ -4049,7 +4060,7 @@
           <t>Xander Nowak</t>
         </is>
       </c>
-      <c r="D61" s="53" t="inlineStr">
+      <c r="D61" s="69" t="inlineStr">
         <is>
           <t>x.nowak@wintergreenbio.com</t>
         </is>
@@ -4097,7 +4108,7 @@
           <t>Quentin Beauchamp</t>
         </is>
       </c>
-      <c r="D62" s="49" t="inlineStr">
+      <c r="D62" s="68" t="inlineStr">
         <is>
           <t>q.beauchamp@yardsleyanalytical.com</t>
         </is>
@@ -4145,7 +4156,7 @@
           <t>Farah Wisniewski</t>
         </is>
       </c>
-      <c r="D63" s="53" t="inlineStr">
+      <c r="D63" s="69" t="inlineStr">
         <is>
           <t>f.wisniewski@zenithbio.com</t>
         </is>
@@ -4193,7 +4204,7 @@
           <t>Pia Marchetti</t>
         </is>
       </c>
-      <c r="D64" s="49" t="inlineStr">
+      <c r="D64" s="68" t="inlineStr">
         <is>
           <t>p.marchetti@wrenfieldscientific.com</t>
         </is>
@@ -4241,7 +4252,7 @@
           <t>Callum Ostrowski</t>
         </is>
       </c>
-      <c r="D65" s="53" t="inlineStr">
+      <c r="D65" s="69" t="inlineStr">
         <is>
           <t>c.ostrowski@everglade-dx.com</t>
         </is>
@@ -4289,7 +4300,7 @@
           <t>Petra Nowak</t>
         </is>
       </c>
-      <c r="D66" s="49" t="inlineStr">
+      <c r="D66" s="68" t="inlineStr">
         <is>
           <t>p.nowak@longacrelabs.com</t>
         </is>
@@ -4337,7 +4348,7 @@
           <t>Lucas Volkov</t>
         </is>
       </c>
-      <c r="D67" s="53" t="inlineStr">
+      <c r="D67" s="69" t="inlineStr">
         <is>
           <t>l.volkov@highfieldinst.com</t>
         </is>
@@ -4385,7 +4396,7 @@
           <t>Noor Delgado</t>
         </is>
       </c>
-      <c r="D68" s="49" t="inlineStr">
+      <c r="D68" s="68" t="inlineStr">
         <is>
           <t>n.delgado@hallmarkmol.com</t>
         </is>
@@ -4433,7 +4444,7 @@
           <t>Kofi Ibori</t>
         </is>
       </c>
-      <c r="D69" s="53" t="inlineStr">
+      <c r="D69" s="69" t="inlineStr">
         <is>
           <t>k.ibori@palladiumassays.com</t>
         </is>
@@ -4481,7 +4492,7 @@
           <t>Lucas Ulrich</t>
         </is>
       </c>
-      <c r="D70" s="49" t="inlineStr">
+      <c r="D70" s="68" t="inlineStr">
         <is>
           <t>l.ulrich@coastwisereagents.com</t>
         </is>
@@ -4529,7 +4540,7 @@
           <t>Umar Sato</t>
         </is>
       </c>
-      <c r="D71" s="53" t="inlineStr">
+      <c r="D71" s="69" t="inlineStr">
         <is>
           <t>u.sato@nettlefordbio.com</t>
         </is>
@@ -4577,7 +4588,7 @@
           <t>Priyanka Janik</t>
         </is>
       </c>
-      <c r="D72" s="49" t="inlineStr">
+      <c r="D72" s="68" t="inlineStr">
         <is>
           <t>p.janik@kadencedx.com</t>
         </is>
@@ -4625,7 +4636,7 @@
           <t>Deepak Iyer</t>
         </is>
       </c>
-      <c r="D73" s="53" t="inlineStr">
+      <c r="D73" s="69" t="inlineStr">
         <is>
           <t>d.iyer@ashlandgx.com</t>
         </is>
@@ -4673,7 +4684,7 @@
           <t>Farah Krishnamurthy</t>
         </is>
       </c>
-      <c r="D74" s="49" t="inlineStr">
+      <c r="D74" s="68" t="inlineStr">
         <is>
           <t>f.krishnamurthy@brixtonreagents.com</t>
         </is>
@@ -4721,7 +4732,7 @@
           <t>Yuki Vukovic</t>
         </is>
       </c>
-      <c r="D75" s="53" t="inlineStr">
+      <c r="D75" s="69" t="inlineStr">
         <is>
           <t>y.vukovic@willowmeredx.com</t>
         </is>
@@ -4769,7 +4780,7 @@
           <t>Vikram Rivas</t>
         </is>
       </c>
-      <c r="D76" s="49" t="inlineStr">
+      <c r="D76" s="68" t="inlineStr">
         <is>
           <t>v.rivas@selbyinst.com</t>
         </is>
@@ -4817,7 +4828,7 @@
           <t>Bianca Vukovic</t>
         </is>
       </c>
-      <c r="D77" s="53" t="inlineStr">
+      <c r="D77" s="69" t="inlineStr">
         <is>
           <t>b.vukovic@thornburybio.com</t>
         </is>
@@ -4865,7 +4876,7 @@
           <t>Selin Ahmed</t>
         </is>
       </c>
-      <c r="D78" s="49" t="inlineStr">
+      <c r="D78" s="68" t="inlineStr">
         <is>
           <t>s.ahmed@argentmol.com</t>
         </is>
@@ -4913,7 +4924,7 @@
           <t>Keiko Rowe</t>
         </is>
       </c>
-      <c r="D79" s="53" t="inlineStr">
+      <c r="D79" s="69" t="inlineStr">
         <is>
           <t>k.rowe@beaconassay.com</t>
         </is>
@@ -4961,7 +4972,7 @@
           <t>Jonas Enescu</t>
         </is>
       </c>
-      <c r="D80" s="49" t="inlineStr">
+      <c r="D80" s="68" t="inlineStr">
         <is>
           <t>j.enescu@coveinst.com</t>
         </is>
@@ -5009,7 +5020,7 @@
           <t>Simone Vasquez</t>
         </is>
       </c>
-      <c r="D81" s="53" t="inlineStr">
+      <c r="D81" s="69" t="inlineStr">
         <is>
           <t>s.vasquez@delaneybio.com</t>
         </is>
@@ -5057,7 +5068,7 @@
           <t>Nikolai Papadopoulos</t>
         </is>
       </c>
-      <c r="D82" s="49" t="inlineStr">
+      <c r="D82" s="68" t="inlineStr">
         <is>
           <t>n.papadopoulos@enfieldreagents.com</t>
         </is>
@@ -5105,7 +5116,7 @@
           <t>Magnus Rivas</t>
         </is>
       </c>
-      <c r="D83" s="53" t="inlineStr">
+      <c r="D83" s="69" t="inlineStr">
         <is>
           <t>m.rivas@fenlanddx.com</t>
         </is>
@@ -5153,7 +5164,7 @@
           <t>Elena Isaev</t>
         </is>
       </c>
-      <c r="D84" s="49" t="inlineStr">
+      <c r="D84" s="68" t="inlineStr">
         <is>
           <t>e.isaev@corvexmol.com</t>
         </is>
@@ -5201,7 +5212,7 @@
           <t>Priyanka Gagnon</t>
         </is>
       </c>
-      <c r="D85" s="53" t="inlineStr">
+      <c r="D85" s="69" t="inlineStr">
         <is>
           <t>p.gagnon@radialbio.com</t>
         </is>
@@ -5249,7 +5260,7 @@
           <t>Henry Radu</t>
         </is>
       </c>
-      <c r="D86" s="49" t="inlineStr">
+      <c r="D86" s="68" t="inlineStr">
         <is>
           <t>h.radu@larkspurbio.com</t>
         </is>
@@ -5297,7 +5308,7 @@
           <t>Wei Onyekachi</t>
         </is>
       </c>
-      <c r="D87" s="53" t="inlineStr">
+      <c r="D87" s="69" t="inlineStr">
         <is>
           <t>w.onyekachi@ashcroftassays.com</t>
         </is>
@@ -5345,7 +5356,7 @@
           <t>Malia Chandra</t>
         </is>
       </c>
-      <c r="D88" s="49" t="inlineStr">
+      <c r="D88" s="68" t="inlineStr">
         <is>
           <t>m.chandra@bellwetherreagents.com</t>
         </is>
@@ -5393,7 +5404,7 @@
           <t>Dahlia Marchand</t>
         </is>
       </c>
-      <c r="D89" s="53" t="inlineStr">
+      <c r="D89" s="69" t="inlineStr">
         <is>
           <t>d.marchand@halcyonanalytical.com</t>
         </is>
@@ -5441,7 +5452,7 @@
           <t>Amir Wisniewski</t>
         </is>
       </c>
-      <c r="D90" s="49" t="inlineStr">
+      <c r="D90" s="68" t="inlineStr">
         <is>
           <t>a.wisniewski@meadowbrookgx.com</t>
         </is>
@@ -5489,7 +5500,7 @@
           <t>Zane Ibori</t>
         </is>
       </c>
-      <c r="D91" s="53" t="inlineStr">
+      <c r="D91" s="69" t="inlineStr">
         <is>
           <t>z.ibori@silverpinetx.com</t>
         </is>
@@ -5537,7 +5548,7 @@
           <t>Leila Cabrera</t>
         </is>
       </c>
-      <c r="D92" s="49" t="inlineStr">
+      <c r="D92" s="68" t="inlineStr">
         <is>
           <t>l.cabrera@windrowsci.com</t>
         </is>
@@ -5585,7 +5596,7 @@
           <t>Cormac Osei</t>
         </is>
       </c>
-      <c r="D93" s="53" t="inlineStr">
+      <c r="D93" s="69" t="inlineStr">
         <is>
           <t>c.osei@norwichbio.com</t>
         </is>
@@ -5633,7 +5644,7 @@
           <t>Cormac Nazarov</t>
         </is>
       </c>
-      <c r="D94" s="49" t="inlineStr">
+      <c r="D94" s="68" t="inlineStr">
         <is>
           <t>c.nazarov@kestreldx.com</t>
         </is>
@@ -5681,7 +5692,7 @@
           <t>Quinn Ainsley</t>
         </is>
       </c>
-      <c r="D95" s="53" t="inlineStr">
+      <c r="D95" s="69" t="inlineStr">
         <is>
           <t>q.ainsley@northgatebiolabs.com</t>
         </is>
@@ -5729,7 +5740,7 @@
           <t>Vikram Nakamura</t>
         </is>
       </c>
-      <c r="D96" s="49" t="inlineStr">
+      <c r="D96" s="68" t="inlineStr">
         <is>
           <t>v.nakamura@sedgwickreagents.com</t>
         </is>
@@ -5777,7 +5788,7 @@
           <t>Klaus Enescu</t>
         </is>
       </c>
-      <c r="D97" s="53" t="inlineStr">
+      <c r="D97" s="69" t="inlineStr">
         <is>
           <t>k.enescu@ashvalemol.com</t>
         </is>
@@ -5825,7 +5836,7 @@
           <t>Vikram Volkov</t>
         </is>
       </c>
-      <c r="D98" s="49" t="inlineStr">
+      <c r="D98" s="68" t="inlineStr">
         <is>
           <t>v.volkov@chartwellinst.com</t>
         </is>
@@ -5873,7 +5884,7 @@
           <t>Larisa Ulrich</t>
         </is>
       </c>
-      <c r="D99" s="53" t="inlineStr">
+      <c r="D99" s="69" t="inlineStr">
         <is>
           <t>l.ulrich@draycottgx.com</t>
         </is>
@@ -5921,7 +5932,7 @@
           <t>Kofi Kapoor</t>
         </is>
       </c>
-      <c r="D100" s="49" t="inlineStr">
+      <c r="D100" s="68" t="inlineStr">
         <is>
           <t>k.kapoor@elmwoodbio.com</t>
         </is>
@@ -5969,7 +5980,7 @@
           <t>Kai Volkov</t>
         </is>
       </c>
-      <c r="D101" s="53" t="inlineStr">
+      <c r="D101" s="69" t="inlineStr">
         <is>
           <t>k.volkov@ferncliffdx.com</t>
         </is>
@@ -6017,7 +6028,7 @@
           <t>Nia Kallas</t>
         </is>
       </c>
-      <c r="D102" s="49" t="inlineStr">
+      <c r="D102" s="68" t="inlineStr">
         <is>
           <t>n.kallas@gairlochanalytical.com</t>
         </is>
@@ -6065,7 +6076,7 @@
           <t>Gustav Tanaka</t>
         </is>
       </c>
-      <c r="D103" s="53" t="inlineStr">
+      <c r="D103" s="69" t="inlineStr">
         <is>
           <t>g.tanaka@harborlightbio.com</t>
         </is>
@@ -6113,7 +6124,7 @@
           <t>Esther Moreau</t>
         </is>
       </c>
-      <c r="D104" s="49" t="inlineStr">
+      <c r="D104" s="68" t="inlineStr">
         <is>
           <t>e.moreau@isleyreagents.com</t>
         </is>
@@ -6161,7 +6172,7 @@
           <t>Ishaan Marchetti</t>
         </is>
       </c>
-      <c r="D105" s="53" t="inlineStr">
+      <c r="D105" s="69" t="inlineStr">
         <is>
           <t>i.marchetti@jerbrookdx.com</t>
         </is>
@@ -6209,7 +6220,7 @@
           <t>Farah Nikolic</t>
         </is>
       </c>
-      <c r="D106" s="49" t="inlineStr">
+      <c r="D106" s="68" t="inlineStr">
         <is>
           <t>f.nikolic@kilburnmol.com</t>
         </is>
@@ -6257,7 +6268,7 @@
           <t>Idris Lundgren</t>
         </is>
       </c>
-      <c r="D107" s="53" t="inlineStr">
+      <c r="D107" s="69" t="inlineStr">
         <is>
           <t>i.lundgren@ledburyassays.com</t>
         </is>
@@ -6305,7 +6316,7 @@
           <t>Oscar Kowalski</t>
         </is>
       </c>
-      <c r="D108" s="49" t="inlineStr">
+      <c r="D108" s="68" t="inlineStr">
         <is>
           <t>o.kowalski@meritbio.com</t>
         </is>
@@ -6353,7 +6364,7 @@
           <t>Elena Radu</t>
         </is>
       </c>
-      <c r="D109" s="53" t="inlineStr">
+      <c r="D109" s="69" t="inlineStr">
         <is>
           <t>e.radu@newburyinst.com</t>
         </is>
@@ -6401,7 +6412,7 @@
           <t>Fiorella Moreau</t>
         </is>
       </c>
-      <c r="D110" s="49" t="inlineStr">
+      <c r="D110" s="68" t="inlineStr">
         <is>
           <t>f.moreau@orleansgx.com</t>
         </is>
@@ -6449,7 +6460,7 @@
           <t>Callum Eriksson</t>
         </is>
       </c>
-      <c r="D111" s="53" t="inlineStr">
+      <c r="D111" s="69" t="inlineStr">
         <is>
           <t>c.eriksson@pembertondx.com</t>
         </is>
@@ -6497,7 +6508,7 @@
           <t>Hana Nikolic</t>
         </is>
       </c>
-      <c r="D112" s="49" t="inlineStr">
+      <c r="D112" s="68" t="inlineStr">
         <is>
           <t>h.nikolic@quentonbiolabs.com</t>
         </is>
@@ -6545,7 +6556,7 @@
           <t>Priyanka Lindqvist</t>
         </is>
       </c>
-      <c r="D113" s="53" t="inlineStr">
+      <c r="D113" s="69" t="inlineStr">
         <is>
           <t>p.lindqvist@ramseyanalytical.com</t>
         </is>
@@ -6593,7 +6604,7 @@
           <t>Edvard Booker</t>
         </is>
       </c>
-      <c r="D114" s="49" t="inlineStr">
+      <c r="D114" s="68" t="inlineStr">
         <is>
           <t>e.booker@sutherlandreagents.com</t>
         </is>
@@ -6641,7 +6652,7 @@
           <t>Yuki Quintero</t>
         </is>
       </c>
-      <c r="D115" s="53" t="inlineStr">
+      <c r="D115" s="69" t="inlineStr">
         <is>
           <t>y.quintero@trellismol.com</t>
         </is>
@@ -6689,7 +6700,7 @@
           <t>Rangi Rowe</t>
         </is>
       </c>
-      <c r="D116" s="49" t="inlineStr">
+      <c r="D116" s="68" t="inlineStr">
         <is>
           <t>r.rowe@underhillbio.com</t>
         </is>
@@ -6737,7 +6748,7 @@
           <t>Aroha Ulrich</t>
         </is>
       </c>
-      <c r="D117" s="53" t="inlineStr">
+      <c r="D117" s="69" t="inlineStr">
         <is>
           <t>a.ulrich@veronaassays.com</t>
         </is>
@@ -6785,7 +6796,7 @@
           <t>Meredith Isaev</t>
         </is>
       </c>
-      <c r="D118" s="49" t="inlineStr">
+      <c r="D118" s="68" t="inlineStr">
         <is>
           <t>m.isaev@whitfielddx.com</t>
         </is>
@@ -6833,7 +6844,7 @@
           <t>Ingrid Isaev</t>
         </is>
       </c>
-      <c r="D119" s="53" t="inlineStr">
+      <c r="D119" s="69" t="inlineStr">
         <is>
           <t>i.isaev@xantheinst.com</t>
         </is>
@@ -6881,7 +6892,7 @@
           <t>Lucas Tanaka</t>
         </is>
       </c>
-      <c r="D120" s="49" t="inlineStr">
+      <c r="D120" s="68" t="inlineStr">
         <is>
           <t>l.tanaka@yorktownbio.com</t>
         </is>
@@ -6929,7 +6940,7 @@
           <t>Sofia Chiu</t>
         </is>
       </c>
-      <c r="D121" s="53" t="inlineStr">
+      <c r="D121" s="69" t="inlineStr">
         <is>
           <t>s.chiu@zephyrgx.com</t>
         </is>
@@ -6977,7 +6988,7 @@
           <t>Kai Quintero</t>
         </is>
       </c>
-      <c r="D122" s="49" t="inlineStr">
+      <c r="D122" s="68" t="inlineStr">
         <is>
           <t>k.quintero@aldermandx.com</t>
         </is>
@@ -7025,7 +7036,7 @@
           <t>Klaus Marchand</t>
         </is>
       </c>
-      <c r="D123" s="53" t="inlineStr">
+      <c r="D123" s="69" t="inlineStr">
         <is>
           <t>k.marchand@bosworthbio.com</t>
         </is>
@@ -7073,7 +7084,7 @@
           <t>Keiko Kapoor</t>
         </is>
       </c>
-      <c r="D124" s="49" t="inlineStr">
+      <c r="D124" s="68" t="inlineStr">
         <is>
           <t>k.kapoor@colvinreagents.com</t>
         </is>
@@ -7121,7 +7132,7 @@
           <t>Selin Wisniewski</t>
         </is>
       </c>
-      <c r="D125" s="53" t="inlineStr">
+      <c r="D125" s="69" t="inlineStr">
         <is>
           <t>s.wisniewski@deerfieldmol.com</t>
         </is>
@@ -7169,7 +7180,7 @@
           <t>Owen Lundgren</t>
         </is>
       </c>
-      <c r="D126" s="49" t="inlineStr">
+      <c r="D126" s="68" t="inlineStr">
         <is>
           <t>o.lundgren@estwickinst.com</t>
         </is>
@@ -7217,7 +7228,7 @@
           <t>Anika Janik</t>
         </is>
       </c>
-      <c r="D127" s="53" t="inlineStr">
+      <c r="D127" s="69" t="inlineStr">
         <is>
           <t>a.janik@fairhavenanalytical.com</t>
         </is>
@@ -7265,7 +7276,7 @@
           <t>Priyanka Radu</t>
         </is>
       </c>
-      <c r="D128" s="49" t="inlineStr">
+      <c r="D128" s="68" t="inlineStr">
         <is>
           <t>p.radu@halewooddx.com</t>
         </is>
@@ -7313,7 +7324,7 @@
           <t>Fiorella Eriksson</t>
         </is>
       </c>
-      <c r="D129" s="53" t="inlineStr">
+      <c r="D129" s="69" t="inlineStr">
         <is>
           <t>f.eriksson@ivywoodassays.com</t>
         </is>
@@ -7361,7 +7372,7 @@
           <t>Petra Terzic</t>
         </is>
       </c>
-      <c r="D130" s="49" t="inlineStr">
+      <c r="D130" s="68" t="inlineStr">
         <is>
           <t>p.terzic@junctionreagents.com</t>
         </is>
@@ -7409,7 +7420,7 @@
           <t>Larisa Ashworth</t>
         </is>
       </c>
-      <c r="D131" s="53" t="inlineStr">
+      <c r="D131" s="69" t="inlineStr">
         <is>
           <t>l.ashworth@keswickgx.com</t>
         </is>
@@ -7457,7 +7468,7 @@
           <t>Wren Ibori</t>
         </is>
       </c>
-      <c r="D132" s="49" t="inlineStr">
+      <c r="D132" s="68" t="inlineStr">
         <is>
           <t>w.ibori@lyndhurstinst.com</t>
         </is>
@@ -7505,7 +7516,7 @@
           <t>Sofia Iyer</t>
         </is>
       </c>
-      <c r="D133" s="53" t="inlineStr">
+      <c r="D133" s="69" t="inlineStr">
         <is>
           <t>s.iyer@marstonbio.com</t>
         </is>
@@ -7553,7 +7564,7 @@
           <t>Larisa Tanaka</t>
         </is>
       </c>
-      <c r="D134" s="49" t="inlineStr">
+      <c r="D134" s="68" t="inlineStr">
         <is>
           <t>l.tanaka@oakenwooddx.com</t>
         </is>
@@ -7601,7 +7612,7 @@
           <t>Dahlia Okafor</t>
         </is>
       </c>
-      <c r="D135" s="53" t="inlineStr">
+      <c r="D135" s="69" t="inlineStr">
         <is>
           <t>d.okafor@pentworthmol.com</t>
         </is>
@@ -7649,7 +7660,7 @@
           <t>Owen Weiss</t>
         </is>
       </c>
-      <c r="D136" s="49" t="inlineStr">
+      <c r="D136" s="68" t="inlineStr">
         <is>
           <t>o.weiss@quaywaterbiolabs.com</t>
         </is>
@@ -7697,7 +7708,7 @@
           <t>Chen Tanaka</t>
         </is>
       </c>
-      <c r="D137" s="53" t="inlineStr">
+      <c r="D137" s="69" t="inlineStr">
         <is>
           <t>c.tanaka@rowtonreagents.com</t>
         </is>
@@ -7745,7 +7756,7 @@
           <t>Tariq Isaev</t>
         </is>
       </c>
-      <c r="D138" s="49" t="inlineStr">
+      <c r="D138" s="68" t="inlineStr">
         <is>
           <t>t.isaev@tavistockassays.com</t>
         </is>
@@ -7793,7 +7804,7 @@
           <t>Kofi Chiu</t>
         </is>
       </c>
-      <c r="D139" s="53" t="inlineStr">
+      <c r="D139" s="69" t="inlineStr">
         <is>
           <t>k.chiu@uxbridgegx.com</t>
         </is>
@@ -7841,7 +7852,7 @@
           <t>Yasmin Yilmaz</t>
         </is>
       </c>
-      <c r="D140" s="49" t="inlineStr">
+      <c r="D140" s="68" t="inlineStr">
         <is>
           <t>y.yilmaz@valloninst.com</t>
         </is>
@@ -7889,7 +7900,7 @@
           <t>Chen Quintero</t>
         </is>
       </c>
-      <c r="D141" s="53" t="inlineStr">
+      <c r="D141" s="69" t="inlineStr">
         <is>
           <t>c.quintero@wintergreenbio.com</t>
         </is>
@@ -7937,7 +7948,7 @@
           <t>Grace Ulrich</t>
         </is>
       </c>
-      <c r="D142" s="49" t="inlineStr">
+      <c r="D142" s="68" t="inlineStr">
         <is>
           <t>g.ulrich@yardsleyanalytical.com</t>
         </is>
@@ -7985,7 +7996,7 @@
           <t>Idris Verma</t>
         </is>
       </c>
-      <c r="D143" s="53" t="inlineStr">
+      <c r="D143" s="69" t="inlineStr">
         <is>
           <t>i.verma@zenithbio.com</t>
         </is>
@@ -8033,7 +8044,7 @@
           <t>Alistair Ostrowski</t>
         </is>
       </c>
-      <c r="D144" s="49" t="inlineStr">
+      <c r="D144" s="68" t="inlineStr">
         <is>
           <t>a.ostrowski@bramfordsci.com</t>
         </is>
@@ -8081,7 +8092,7 @@
           <t>Paloma Booker</t>
         </is>
       </c>
-      <c r="D145" s="53" t="inlineStr">
+      <c r="D145" s="69" t="inlineStr">
         <is>
           <t>p.booker@everglade-dx.com</t>
         </is>
@@ -8129,7 +8140,7 @@
           <t>Vikram Ostrowski</t>
         </is>
       </c>
-      <c r="D146" s="49" t="inlineStr">
+      <c r="D146" s="68" t="inlineStr">
         <is>
           <t>v.ostrowski@longacrelabs.com</t>
         </is>
@@ -8177,7 +8188,7 @@
           <t>Nathan Castellanos</t>
         </is>
       </c>
-      <c r="D147" s="53" t="inlineStr">
+      <c r="D147" s="69" t="inlineStr">
         <is>
           <t>n.castellanos@highfieldinst.com</t>
         </is>
@@ -8225,7 +8236,7 @@
           <t>Amelia Moreau</t>
         </is>
       </c>
-      <c r="D148" s="49" t="inlineStr">
+      <c r="D148" s="68" t="inlineStr">
         <is>
           <t>a.moreau@hallmarkmol.com</t>
         </is>
@@ -8273,7 +8284,7 @@
           <t>Ximena Nowak</t>
         </is>
       </c>
-      <c r="D149" s="53" t="inlineStr">
+      <c r="D149" s="69" t="inlineStr">
         <is>
           <t>x.nowak@palladiumassays.com</t>
         </is>
@@ -8321,7 +8332,7 @@
           <t>Torsten Wei</t>
         </is>
       </c>
-      <c r="D150" s="49" t="inlineStr">
+      <c r="D150" s="68" t="inlineStr">
         <is>
           <t>t.wei@coastwisereagents.com</t>
         </is>
@@ -8369,7 +8380,7 @@
           <t>Boris Sato</t>
         </is>
       </c>
-      <c r="D151" s="53" t="inlineStr">
+      <c r="D151" s="69" t="inlineStr">
         <is>
           <t>b.sato@nettlefordbio.com</t>
         </is>
@@ -8417,7 +8428,7 @@
           <t>Fatima Hoffmann</t>
         </is>
       </c>
-      <c r="D152" s="49" t="inlineStr">
+      <c r="D152" s="68" t="inlineStr">
         <is>
           <t>f.hoffmann@kadencedx.com</t>
         </is>
@@ -8465,7 +8476,7 @@
           <t>Sanjay Dahl</t>
         </is>
       </c>
-      <c r="D153" s="53" t="inlineStr">
+      <c r="D153" s="69" t="inlineStr">
         <is>
           <t>s.dahl@ashlandgx.com</t>
         </is>
@@ -8513,7 +8524,7 @@
           <t>Amir Kapoor</t>
         </is>
       </c>
-      <c r="D154" s="49" t="inlineStr">
+      <c r="D154" s="68" t="inlineStr">
         <is>
           <t>a.kapoor@brixtonreagents.com</t>
         </is>
@@ -8561,7 +8572,7 @@
           <t>Nikolai Radu</t>
         </is>
       </c>
-      <c r="D155" s="53" t="inlineStr">
+      <c r="D155" s="69" t="inlineStr">
         <is>
           <t>n.radu@willowmeredx.com</t>
         </is>
@@ -8609,7 +8620,7 @@
           <t>Vera Zajac</t>
         </is>
       </c>
-      <c r="D156" s="49" t="inlineStr">
+      <c r="D156" s="68" t="inlineStr">
         <is>
           <t>v.zajac@selbyinst.com</t>
         </is>
@@ -8657,7 +8668,7 @@
           <t>Malia Moreau</t>
         </is>
       </c>
-      <c r="D157" s="53" t="inlineStr">
+      <c r="D157" s="69" t="inlineStr">
         <is>
           <t>m.moreau@caldwelldx.com</t>
         </is>
@@ -8705,7 +8716,7 @@
           <t>Bianca Nowak</t>
         </is>
       </c>
-      <c r="D158" s="49" t="inlineStr">
+      <c r="D158" s="68" t="inlineStr">
         <is>
           <t>b.nowak@thornburybio.com</t>
         </is>
@@ -8753,7 +8764,7 @@
           <t>Umar Yilmaz</t>
         </is>
       </c>
-      <c r="D159" s="53" t="inlineStr">
+      <c r="D159" s="69" t="inlineStr">
         <is>
           <t>u.yilmaz@argentmol.com</t>
         </is>
@@ -8801,7 +8812,7 @@
           <t>Oscar Sharma</t>
         </is>
       </c>
-      <c r="D160" s="49" t="inlineStr">
+      <c r="D160" s="68" t="inlineStr">
         <is>
           <t>o.sharma@beaconassay.com</t>
         </is>
@@ -8849,7 +8860,7 @@
           <t>Kenji Ferreira</t>
         </is>
       </c>
-      <c r="D161" s="53" t="inlineStr">
+      <c r="D161" s="69" t="inlineStr">
         <is>
           <t>k.ferreira@coveinst.com</t>
         </is>
@@ -8897,7 +8908,7 @@
           <t>Jamal Kapoor</t>
         </is>
       </c>
-      <c r="D162" s="49" t="inlineStr">
+      <c r="D162" s="68" t="inlineStr">
         <is>
           <t>j.kapoor@delaneybio.com</t>
         </is>
@@ -8945,7 +8956,7 @@
           <t>Henry Moreau</t>
         </is>
       </c>
-      <c r="D163" s="53" t="inlineStr">
+      <c r="D163" s="69" t="inlineStr">
         <is>
           <t>h.moreau@enfieldreagents.com</t>
         </is>
@@ -8993,7 +9004,7 @@
           <t>Cormac Sato</t>
         </is>
       </c>
-      <c r="D164" s="49" t="inlineStr">
+      <c r="D164" s="68" t="inlineStr">
         <is>
           <t>c.sato@fenlanddx.com</t>
         </is>
@@ -9041,7 +9052,7 @@
           <t>Neha Farouk</t>
         </is>
       </c>
-      <c r="D165" s="53" t="inlineStr">
+      <c r="D165" s="69" t="inlineStr">
         <is>
           <t>n.farouk@corvexmol.com</t>
         </is>
@@ -9089,7 +9100,7 @@
           <t>Alistair Osei</t>
         </is>
       </c>
-      <c r="D166" s="49" t="inlineStr">
+      <c r="D166" s="68" t="inlineStr">
         <is>
           <t>a.osei@radialbio.com</t>
         </is>
@@ -9137,7 +9148,7 @@
           <t>Selin Solheim</t>
         </is>
       </c>
-      <c r="D167" s="53" t="inlineStr">
+      <c r="D167" s="69" t="inlineStr">
         <is>
           <t>s.solheim@larkspurbio.com</t>
         </is>
@@ -9185,7 +9196,7 @@
           <t>Hana Janik</t>
         </is>
       </c>
-      <c r="D168" s="49" t="inlineStr">
+      <c r="D168" s="68" t="inlineStr">
         <is>
           <t>h.janik@ashcroftassays.com</t>
         </is>
@@ -9233,7 +9244,7 @@
           <t>Ivaan Winterbourne</t>
         </is>
       </c>
-      <c r="D169" s="53" t="inlineStr">
+      <c r="D169" s="69" t="inlineStr">
         <is>
           <t>i.winterbourne@bellwetherreagents.com</t>
         </is>
@@ -9281,7 +9292,7 @@
           <t>Imani Ferreira</t>
         </is>
       </c>
-      <c r="D170" s="49" t="inlineStr">
+      <c r="D170" s="68" t="inlineStr">
         <is>
           <t>i.ferreira@halcyonanalytical.com</t>
         </is>
@@ -9329,7 +9340,7 @@
           <t>Tariq Beaulieu</t>
         </is>
       </c>
-      <c r="D171" s="53" t="inlineStr">
+      <c r="D171" s="69" t="inlineStr">
         <is>
           <t>t.beaulieu@meadowbrookgx.com</t>
         </is>
@@ -9377,7 +9388,7 @@
           <t>Sofia Sokolov</t>
         </is>
       </c>
-      <c r="D172" s="49" t="inlineStr">
+      <c r="D172" s="68" t="inlineStr">
         <is>
           <t>s.sokolov@silverpinetx.com</t>
         </is>
@@ -9425,7 +9436,7 @@
           <t>Imani Ostrowski</t>
         </is>
       </c>
-      <c r="D173" s="53" t="inlineStr">
+      <c r="D173" s="69" t="inlineStr">
         <is>
           <t>i.ostrowski@windrowsci.com</t>
         </is>
@@ -9473,7 +9484,7 @@
           <t>Sofia Tanaka</t>
         </is>
       </c>
-      <c r="D174" s="49" t="inlineStr">
+      <c r="D174" s="68" t="inlineStr">
         <is>
           <t>s.tanaka@norwichbio.com</t>
         </is>
@@ -9521,7 +9532,7 @@
           <t>Aisha Larsen</t>
         </is>
       </c>
-      <c r="D175" s="53" t="inlineStr">
+      <c r="D175" s="69" t="inlineStr">
         <is>
           <t>a.larsen@kestreldx.com</t>
         </is>
@@ -9569,7 +9580,7 @@
           <t>Leila Ainsley</t>
         </is>
       </c>
-      <c r="D176" s="49" t="inlineStr">
+      <c r="D176" s="68" t="inlineStr">
         <is>
           <t>l.ainsley@northgatebiolabs.com</t>
         </is>
@@ -9617,7 +9628,7 @@
           <t>Ingrid Verma</t>
         </is>
       </c>
-      <c r="D177" s="53" t="inlineStr">
+      <c r="D177" s="69" t="inlineStr">
         <is>
           <t>i.verma@sedgwickreagents.com</t>
         </is>
@@ -9665,7 +9676,7 @@
           <t>Renata Osei</t>
         </is>
       </c>
-      <c r="D178" s="49" t="inlineStr">
+      <c r="D178" s="68" t="inlineStr">
         <is>
           <t>r.osei@ashvalemol.com</t>
         </is>
@@ -9713,7 +9724,7 @@
           <t>Priyanka Quintero</t>
         </is>
       </c>
-      <c r="D179" s="53" t="inlineStr">
+      <c r="D179" s="69" t="inlineStr">
         <is>
           <t>p.quintero@chartwellinst.com</t>
         </is>
@@ -9761,7 +9772,7 @@
           <t>Rohit Wei</t>
         </is>
       </c>
-      <c r="D180" s="49" t="inlineStr">
+      <c r="D180" s="68" t="inlineStr">
         <is>
           <t>r.wei@draycottgx.com</t>
         </is>
@@ -9809,7 +9820,7 @@
           <t>Magnus Manaia</t>
         </is>
       </c>
-      <c r="D181" s="53" t="inlineStr">
+      <c r="D181" s="69" t="inlineStr">
         <is>
           <t>m.manaia@elmwoodbio.com</t>
         </is>
@@ -9857,7 +9868,7 @@
           <t>Freya Nazarov</t>
         </is>
       </c>
-      <c r="D182" s="49" t="inlineStr">
+      <c r="D182" s="68" t="inlineStr">
         <is>
           <t>f.nazarov@ferncliffdx.com</t>
         </is>
@@ -9905,7 +9916,7 @@
           <t>Viktor Beringer</t>
         </is>
       </c>
-      <c r="D183" s="53" t="inlineStr">
+      <c r="D183" s="69" t="inlineStr">
         <is>
           <t>v.beringer@gairlochanalytical.com</t>
         </is>
@@ -9953,7 +9964,7 @@
           <t>Klaus Lindqvist</t>
         </is>
       </c>
-      <c r="D184" s="49" t="inlineStr">
+      <c r="D184" s="68" t="inlineStr">
         <is>
           <t>k.lindqvist@harborlightbio.com</t>
         </is>
@@ -10001,7 +10012,7 @@
           <t>Gustav Zajac</t>
         </is>
       </c>
-      <c r="D185" s="53" t="inlineStr">
+      <c r="D185" s="69" t="inlineStr">
         <is>
           <t>g.zajac@isleyreagents.com</t>
         </is>
@@ -10049,7 +10060,7 @@
           <t>Freya Kekoa</t>
         </is>
       </c>
-      <c r="D186" s="49" t="inlineStr">
+      <c r="D186" s="68" t="inlineStr">
         <is>
           <t>f.kekoa@jerbrookdx.com</t>
         </is>
@@ -10097,7 +10108,7 @@
           <t>Umar Chandra</t>
         </is>
       </c>
-      <c r="D187" s="53" t="inlineStr">
+      <c r="D187" s="69" t="inlineStr">
         <is>
           <t>u.chandra@kilburnmol.com</t>
         </is>
@@ -10145,7 +10156,7 @@
           <t>Marcus Cortez</t>
         </is>
       </c>
-      <c r="D188" s="49" t="inlineStr">
+      <c r="D188" s="68" t="inlineStr">
         <is>
           <t>m.cortez@ledburyassays.com</t>
         </is>
@@ -10193,7 +10204,7 @@
           <t>Malia Lombardi</t>
         </is>
       </c>
-      <c r="D189" s="53" t="inlineStr">
+      <c r="D189" s="69" t="inlineStr">
         <is>
           <t>m.lombardi@meritbio.com</t>
         </is>
@@ -10241,7 +10252,7 @@
           <t>Cormac Terzic</t>
         </is>
       </c>
-      <c r="D190" s="49" t="inlineStr">
+      <c r="D190" s="68" t="inlineStr">
         <is>
           <t>c.terzic@newburyinst.com</t>
         </is>
@@ -10289,7 +10300,7 @@
           <t>Grace Lombardi</t>
         </is>
       </c>
-      <c r="D191" s="53" t="inlineStr">
+      <c r="D191" s="69" t="inlineStr">
         <is>
           <t>g.lombardi@orleansgx.com</t>
         </is>
@@ -10337,7 +10348,7 @@
           <t>Amelia Nakamura</t>
         </is>
       </c>
-      <c r="D192" s="49" t="inlineStr">
+      <c r="D192" s="68" t="inlineStr">
         <is>
           <t>a.nakamura@pembertondx.com</t>
         </is>
@@ -10385,7 +10396,7 @@
           <t>Nadia Quintero</t>
         </is>
       </c>
-      <c r="D193" s="53" t="inlineStr">
+      <c r="D193" s="69" t="inlineStr">
         <is>
           <t>n.quintero@quentonbiolabs.com</t>
         </is>
@@ -10433,7 +10444,7 @@
           <t>Tariq Vasquez</t>
         </is>
       </c>
-      <c r="D194" s="49" t="inlineStr">
+      <c r="D194" s="68" t="inlineStr">
         <is>
           <t>t.vasquez@ramseyanalytical.com</t>
         </is>
@@ -10481,7 +10492,7 @@
           <t>Nia Chiu</t>
         </is>
       </c>
-      <c r="D195" s="53" t="inlineStr">
+      <c r="D195" s="69" t="inlineStr">
         <is>
           <t>n.chiu@sutherlandreagents.com</t>
         </is>
@@ -10529,7 +10540,7 @@
           <t>Amir Petrov</t>
         </is>
       </c>
-      <c r="D196" s="49" t="inlineStr">
+      <c r="D196" s="68" t="inlineStr">
         <is>
           <t>a.petrov@trellismol.com</t>
         </is>
@@ -10577,7 +10588,7 @@
           <t>Chen Ustinov</t>
         </is>
       </c>
-      <c r="D197" s="53" t="inlineStr">
+      <c r="D197" s="69" t="inlineStr">
         <is>
           <t>c.ustinov@underhillbio.com</t>
         </is>
@@ -10625,7 +10636,7 @@
           <t>Oscar Kapoor</t>
         </is>
       </c>
-      <c r="D198" s="49" t="inlineStr">
+      <c r="D198" s="68" t="inlineStr">
         <is>
           <t>o.kapoor@veronaassays.com</t>
         </is>
@@ -10673,7 +10684,7 @@
           <t>Jovana Kapoor</t>
         </is>
       </c>
-      <c r="D199" s="53" t="inlineStr">
+      <c r="D199" s="69" t="inlineStr">
         <is>
           <t>j.kapoor@whitfielddx.com</t>
         </is>
@@ -10721,7 +10732,7 @@
           <t>Hana Haddad</t>
         </is>
       </c>
-      <c r="D200" s="49" t="inlineStr">
+      <c r="D200" s="68" t="inlineStr">
         <is>
           <t>h.haddad@xantheinst.com</t>
         </is>
@@ -10769,7 +10780,7 @@
           <t>Zara Nowak</t>
         </is>
       </c>
-      <c r="D201" s="53" t="inlineStr">
+      <c r="D201" s="69" t="inlineStr">
         <is>
           <t>z.nowak@yorktownbio.com</t>
         </is>
@@ -10817,7 +10828,7 @@
           <t>Priya Al-Sayed</t>
         </is>
       </c>
-      <c r="D202" s="49" t="inlineStr">
+      <c r="D202" s="68" t="inlineStr">
         <is>
           <t>p.al-sayed@zephyrgx.com</t>
         </is>
@@ -10865,7 +10876,7 @@
           <t>Yasmin Grondin</t>
         </is>
       </c>
-      <c r="D203" s="53" t="inlineStr">
+      <c r="D203" s="69" t="inlineStr">
         <is>
           <t>y.grondin@aldermandx.com</t>
         </is>
@@ -10913,7 +10924,7 @@
           <t>Mikhail Yilmaz</t>
         </is>
       </c>
-      <c r="D204" s="49" t="inlineStr">
+      <c r="D204" s="68" t="inlineStr">
         <is>
           <t>m.yilmaz@bosworthbio.com</t>
         </is>
@@ -10961,7 +10972,7 @@
           <t>Amir Mancini</t>
         </is>
       </c>
-      <c r="D205" s="53" t="inlineStr">
+      <c r="D205" s="69" t="inlineStr">
         <is>
           <t>a.mancini@colvinreagents.com</t>
         </is>
@@ -11009,7 +11020,7 @@
           <t>Vera Falcon</t>
         </is>
       </c>
-      <c r="D206" s="49" t="inlineStr">
+      <c r="D206" s="68" t="inlineStr">
         <is>
           <t>v.falcon@deerfieldmol.com</t>
         </is>
@@ -11057,7 +11068,7 @@
           <t>Oscar Farouk</t>
         </is>
       </c>
-      <c r="D207" s="53" t="inlineStr">
+      <c r="D207" s="69" t="inlineStr">
         <is>
           <t>o.farouk@estwickinst.com</t>
         </is>
@@ -11105,7 +11116,7 @@
           <t>Boris Grondin</t>
         </is>
       </c>
-      <c r="D208" s="49" t="inlineStr">
+      <c r="D208" s="68" t="inlineStr">
         <is>
           <t>b.grondin@fairhavenanalytical.com</t>
         </is>
@@ -11153,7 +11164,7 @@
           <t>Torsten Orozco</t>
         </is>
       </c>
-      <c r="D209" s="53" t="inlineStr">
+      <c r="D209" s="69" t="inlineStr">
         <is>
           <t>t.orozco@glenridgebiolabs.com</t>
         </is>
@@ -11201,7 +11212,7 @@
           <t>Kenji Okafor</t>
         </is>
       </c>
-      <c r="D210" s="49" t="inlineStr">
+      <c r="D210" s="68" t="inlineStr">
         <is>
           <t>k.okafor@halewooddx.com</t>
         </is>
@@ -11249,7 +11260,7 @@
           <t>Jamal Wei</t>
         </is>
       </c>
-      <c r="D211" s="53" t="inlineStr">
+      <c r="D211" s="69" t="inlineStr">
         <is>
           <t>j.wei@ivywoodassays.com</t>
         </is>
